--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_business_consumer_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="adx_bayanat" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,26 +589,23 @@
           <t>Business &amp; Consumer Services</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.215</v>
-      </c>
       <c r="G2">
-        <v>-0.7182103610675039</v>
+        <v>0.1683642899940084</v>
       </c>
       <c r="H2">
-        <v>-0.7182103610675039</v>
+        <v>0.1683642899940084</v>
       </c>
       <c r="I2">
-        <v>-0.7260596546310831</v>
+        <v>0.32893948472139</v>
       </c>
       <c r="J2">
-        <v>-0.7260596546310831</v>
+        <v>0.32893948472139</v>
       </c>
       <c r="K2">
-        <v>-96.8</v>
+        <v>51.8</v>
       </c>
       <c r="L2">
-        <v>-0.7598116169544741</v>
+        <v>0.3103654883163571</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +623,64 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>49.1</v>
+        <v>31.2</v>
       </c>
       <c r="V2">
-        <v>1.631229235880399</v>
-      </c>
-      <c r="W2">
-        <v>-0.6381015161502966</v>
+        <v>0.009095149253731344</v>
       </c>
       <c r="X2">
-        <v>0.09689267974120909</v>
-      </c>
-      <c r="Y2">
-        <v>-0.7349941958915057</v>
-      </c>
-      <c r="Z2">
-        <v>0.8834338811455517</v>
-      </c>
-      <c r="AA2">
-        <v>-0.6414256986339366</v>
+        <v>0.1067402836811948</v>
       </c>
       <c r="AB2">
-        <v>0.04608072406343071</v>
-      </c>
-      <c r="AC2">
-        <v>-0.6875064226973673</v>
+        <v>0.1065481805148944</v>
       </c>
       <c r="AD2">
-        <v>50.6</v>
+        <v>15.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>50.6</v>
+        <v>15.8</v>
       </c>
       <c r="AG2">
-        <v>1.5</v>
+        <v>-15.4</v>
       </c>
       <c r="AH2">
-        <v>0.6270136307311028</v>
+        <v>0.004584760025535372</v>
       </c>
       <c r="AI2">
-        <v>0.6148238153098421</v>
+        <v>0.12609736632083</v>
       </c>
       <c r="AJ2">
-        <v>0.04746835443037974</v>
+        <v>-0.004509516837481698</v>
       </c>
       <c r="AK2">
-        <v>0.04518072289156626</v>
+        <v>-0.1636556854410202</v>
       </c>
       <c r="AL2">
-        <v>4.68</v>
+        <v>0.774</v>
       </c>
       <c r="AM2">
-        <v>4.326</v>
+        <v>0.774</v>
       </c>
       <c r="AN2">
-        <v>-0.5863267670915412</v>
+        <v>0.2743055555555556</v>
       </c>
       <c r="AO2">
-        <v>-19.76495726495727</v>
+        <v>70.93023255813954</v>
       </c>
       <c r="AP2">
-        <v>-0.01738122827346466</v>
+        <v>-0.2673611111111111</v>
       </c>
       <c r="AQ2">
-        <v>-21.38233934350439</v>
+        <v>70.93023255813954</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +691,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Depa PLC (DIFX:DEPA)</t>
+          <t>Bayanat AI PLC (ADX:BAYANAT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,26 +699,23 @@
           <t>Business &amp; Consumer Services</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.215</v>
-      </c>
       <c r="G3">
-        <v>-0.7182103610675039</v>
+        <v>0.1683642899940084</v>
       </c>
       <c r="H3">
-        <v>-0.7182103610675039</v>
+        <v>0.1683642899940084</v>
       </c>
       <c r="I3">
-        <v>-0.7260596546310831</v>
+        <v>0.32893948472139</v>
       </c>
       <c r="J3">
-        <v>-0.7260596546310831</v>
+        <v>0.32893948472139</v>
       </c>
       <c r="K3">
-        <v>-96.8</v>
+        <v>51.8</v>
       </c>
       <c r="L3">
-        <v>-0.7598116169544741</v>
+        <v>0.3103654883163571</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +724,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +733,8776 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>49.1</v>
+        <v>31.2</v>
       </c>
       <c r="V3">
-        <v>1.631229235880399</v>
+        <v>0.009095149253731344</v>
+      </c>
+      <c r="X3">
+        <v>0.1067402836811948</v>
+      </c>
+      <c r="AB3">
+        <v>0.1065481805148944</v>
+      </c>
+      <c r="AD3">
+        <v>15.8</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>15.8</v>
+      </c>
+      <c r="AG3">
+        <v>-15.4</v>
+      </c>
+      <c r="AH3">
+        <v>0.004584760025535372</v>
+      </c>
+      <c r="AI3">
+        <v>0.12609736632083</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.004509516837481698</v>
+      </c>
+      <c r="AK3">
+        <v>-0.1636556854410202</v>
+      </c>
+      <c r="AL3">
+        <v>0.774</v>
+      </c>
+      <c r="AM3">
+        <v>0.774</v>
+      </c>
+      <c r="AN3">
+        <v>0.2743055555555556</v>
+      </c>
+      <c r="AO3">
+        <v>70.93023255813954</v>
+      </c>
+      <c r="AP3">
+        <v>-0.2673611111111111</v>
+      </c>
+      <c r="AQ3">
+        <v>70.93023255813954</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bayanat AI PLC (ADX:BAYANAT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADX:BAYANAT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Business &amp; Consumer Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.00458476002553537</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3430.4</v>
+      </c>
+      <c r="H2">
+        <v>3452.22858134315</v>
+      </c>
+      <c r="I2">
+        <v>3415</v>
+      </c>
+      <c r="J2">
+        <v>3421.02858134315</v>
+      </c>
+      <c r="K2">
+        <v>15.8</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.106548180514894</v>
+      </c>
+      <c r="N2">
+        <v>0.10642879378445</v>
+      </c>
+      <c r="O2">
+        <v>0.0648399082568807</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.106740283681195</v>
+      </c>
+      <c r="T2">
+        <v>0.10642879378445</v>
+      </c>
+      <c r="U2">
+        <v>1.00410622765268</v>
+      </c>
+      <c r="V2">
+        <v>0.999502641558744</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>3430.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.06766244627325971</v>
+      </c>
+      <c r="AC2">
+        <v>0.06483990825688074</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>57.6</v>
+      </c>
+      <c r="AH2">
+        <v>1.35</v>
+      </c>
+      <c r="AI2">
+        <v>3.389999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>15.8</v>
+      </c>
+      <c r="AK2">
+        <v>15.8</v>
+      </c>
+      <c r="AL2">
+        <v>0.774</v>
+      </c>
+      <c r="AM2">
+        <v>15.8</v>
+      </c>
+      <c r="AN2">
+        <v>31.2</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1064287937844497</v>
+      </c>
+      <c r="C2">
+        <v>3452.228581343153</v>
+      </c>
+      <c r="D2">
+        <v>3421.028581343153</v>
+      </c>
+      <c r="E2">
+        <v>-15.8</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>31.2</v>
+      </c>
+      <c r="H2">
+        <v>3430.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>57.6</v>
+      </c>
+      <c r="K2">
+        <v>1.35</v>
+      </c>
+      <c r="L2">
+        <v>56.25</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>56.25</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>56.25</v>
+      </c>
+      <c r="Q2">
+        <v>57.6</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1064287937844497</v>
+      </c>
+      <c r="T2">
+        <v>0.9995026415587442</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1064977937844497</v>
+      </c>
+      <c r="C3">
+        <v>3414.279747298541</v>
+      </c>
+      <c r="D3">
+        <v>3417.541747298541</v>
+      </c>
+      <c r="E3">
+        <v>18.662</v>
+      </c>
+      <c r="F3">
+        <v>34.462</v>
+      </c>
+      <c r="G3">
+        <v>31.2</v>
+      </c>
+      <c r="H3">
+        <v>3430.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>57.6</v>
+      </c>
+      <c r="K3">
+        <v>1.35</v>
+      </c>
+      <c r="L3">
+        <v>56.25</v>
+      </c>
+      <c r="M3">
+        <v>1.5749134</v>
+      </c>
+      <c r="N3">
+        <v>54.6750866</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>54.6750866</v>
+      </c>
+      <c r="Q3">
+        <v>56.0250866</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1071119129135855</v>
+      </c>
+      <c r="T3">
+        <v>1.009598627837115</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.6381015161502966</v>
-      </c>
-      <c r="X3">
-        <v>0.09689267974120909</v>
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.7349941958915057</v>
+        <v>35.71624954108587</v>
       </c>
       <c r="Z3">
-        <v>0.8834338811455517</v>
-      </c>
-      <c r="AA3">
-        <v>-0.6414256986339366</v>
-      </c>
-      <c r="AB3">
-        <v>0.04608072406343071</v>
-      </c>
-      <c r="AC3">
-        <v>-0.6875064226973673</v>
-      </c>
-      <c r="AD3">
-        <v>50.6</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>50.6</v>
-      </c>
-      <c r="AG3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1065667937844497</v>
+      </c>
+      <c r="C4">
+        <v>3376.338013827402</v>
+      </c>
+      <c r="D4">
+        <v>3414.062013827402</v>
+      </c>
+      <c r="E4">
+        <v>53.12400000000001</v>
+      </c>
+      <c r="F4">
+        <v>68.92400000000001</v>
+      </c>
+      <c r="G4">
+        <v>31.2</v>
+      </c>
+      <c r="H4">
+        <v>3430.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>57.6</v>
+      </c>
+      <c r="K4">
+        <v>1.35</v>
+      </c>
+      <c r="L4">
+        <v>56.25</v>
+      </c>
+      <c r="M4">
+        <v>3.1498268</v>
+      </c>
+      <c r="N4">
+        <v>53.1001732</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>53.1001732</v>
+      </c>
+      <c r="Q4">
+        <v>54.4501732</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1078089732494385</v>
+      </c>
+      <c r="T4">
+        <v>1.01990065465178</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0457</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>17.85812477054294</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1066837937844497</v>
+      </c>
+      <c r="C5">
+        <v>3335.991763208084</v>
+      </c>
+      <c r="D5">
+        <v>3408.177763208084</v>
+      </c>
+      <c r="E5">
+        <v>87.58600000000001</v>
+      </c>
+      <c r="F5">
+        <v>103.386</v>
+      </c>
+      <c r="G5">
+        <v>31.2</v>
+      </c>
+      <c r="H5">
+        <v>3430.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>57.6</v>
+      </c>
+      <c r="K5">
+        <v>1.35</v>
+      </c>
+      <c r="L5">
+        <v>56.25</v>
+      </c>
+      <c r="M5">
+        <v>4.890157800000001</v>
+      </c>
+      <c r="N5">
+        <v>51.3598422</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>51.3598422</v>
+      </c>
+      <c r="Q5">
+        <v>52.7098422</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1085204059633502</v>
+      </c>
+      <c r="T5">
+        <v>1.030415094390458</v>
+      </c>
+      <c r="U5">
+        <v>0.0473</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.0473</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>11.50269629335888</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1069207937844497</v>
+      </c>
+      <c r="C6">
+        <v>3289.672324605177</v>
+      </c>
+      <c r="D6">
+        <v>3396.320324605178</v>
+      </c>
+      <c r="E6">
+        <v>122.048</v>
+      </c>
+      <c r="F6">
+        <v>137.848</v>
+      </c>
+      <c r="G6">
+        <v>31.2</v>
+      </c>
+      <c r="H6">
+        <v>3430.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>57.6</v>
+      </c>
+      <c r="K6">
+        <v>1.35</v>
+      </c>
+      <c r="L6">
+        <v>56.25</v>
+      </c>
+      <c r="M6">
+        <v>7.044032800000001</v>
+      </c>
+      <c r="N6">
+        <v>49.2059672</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>49.2059672</v>
+      </c>
+      <c r="Q6">
+        <v>50.5559672</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1092466601921351</v>
+      </c>
+      <c r="T6">
+        <v>1.041148584957025</v>
+      </c>
+      <c r="U6">
+        <v>0.0511</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.0511</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>7.985482407180158</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1072387937844497</v>
+      </c>
+      <c r="C7">
+        <v>3239.429364662692</v>
+      </c>
+      <c r="D7">
+        <v>3380.539364662692</v>
+      </c>
+      <c r="E7">
+        <v>156.51</v>
+      </c>
+      <c r="F7">
+        <v>172.31</v>
+      </c>
+      <c r="G7">
+        <v>31.2</v>
+      </c>
+      <c r="H7">
+        <v>3430.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>57.6</v>
+      </c>
+      <c r="K7">
+        <v>1.35</v>
+      </c>
+      <c r="L7">
+        <v>56.25</v>
+      </c>
+      <c r="M7">
+        <v>9.477050000000002</v>
+      </c>
+      <c r="N7">
+        <v>46.77294999999999</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>46.77294999999999</v>
+      </c>
+      <c r="Q7">
+        <v>48.12295</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1099882039836313</v>
+      </c>
+      <c r="T7">
+        <v>1.052108043746047</v>
+      </c>
+      <c r="U7">
+        <v>0.055</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.055</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>5.935391287373179</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1074007937844497</v>
+      </c>
+      <c r="C8">
+        <v>3196.984259120268</v>
+      </c>
+      <c r="D8">
+        <v>3372.556259120268</v>
+      </c>
+      <c r="E8">
+        <v>190.972</v>
+      </c>
+      <c r="F8">
+        <v>206.772</v>
+      </c>
+      <c r="G8">
+        <v>31.2</v>
+      </c>
+      <c r="H8">
+        <v>3430.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>57.6</v>
+      </c>
+      <c r="K8">
+        <v>1.35</v>
+      </c>
+      <c r="L8">
+        <v>56.25</v>
+      </c>
+      <c r="M8">
+        <v>11.37246</v>
+      </c>
+      <c r="N8">
+        <v>44.87754</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>44.87754</v>
+      </c>
+      <c r="Q8">
+        <v>46.22754</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.110745525302606</v>
+      </c>
+      <c r="T8">
+        <v>1.063300682509302</v>
+      </c>
+      <c r="U8">
+        <v>0.055</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.055</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>4.946159406144316</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1081227937844497</v>
+      </c>
+      <c r="C9">
+        <v>3127.39693473337</v>
+      </c>
+      <c r="D9">
+        <v>3337.430934733371</v>
+      </c>
+      <c r="E9">
+        <v>225.434</v>
+      </c>
+      <c r="F9">
+        <v>241.234</v>
+      </c>
+      <c r="G9">
+        <v>31.2</v>
+      </c>
+      <c r="H9">
+        <v>3430.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>57.6</v>
+      </c>
+      <c r="K9">
+        <v>1.35</v>
+      </c>
+      <c r="L9">
+        <v>56.25</v>
+      </c>
+      <c r="M9">
+        <v>15.197742</v>
+      </c>
+      <c r="N9">
+        <v>41.05225799999999</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>41.05225799999999</v>
+      </c>
+      <c r="Q9">
+        <v>42.402258</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1115191331015588</v>
+      </c>
+      <c r="T9">
+        <v>1.074734023181445</v>
+      </c>
+      <c r="U9">
+        <v>0.063</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.063</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>3.701207718883502</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1106367937844497</v>
+      </c>
+      <c r="C10">
+        <v>2976.138221963932</v>
+      </c>
+      <c r="D10">
+        <v>3220.634221963932</v>
+      </c>
+      <c r="E10">
+        <v>259.896</v>
+      </c>
+      <c r="F10">
+        <v>275.696</v>
+      </c>
+      <c r="G10">
+        <v>31.2</v>
+      </c>
+      <c r="H10">
+        <v>3430.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>57.6</v>
+      </c>
+      <c r="K10">
+        <v>1.35</v>
+      </c>
+      <c r="L10">
+        <v>56.25</v>
+      </c>
+      <c r="M10">
+        <v>25.1986144</v>
+      </c>
+      <c r="N10">
+        <v>31.0513856</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>31.0513856</v>
+      </c>
+      <c r="Q10">
+        <v>32.4013856</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1123095584613584</v>
+      </c>
+      <c r="T10">
+        <v>1.086415914737765</v>
+      </c>
+      <c r="U10">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>2.232265596317867</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1130617937844497</v>
+      </c>
+      <c r="C11">
+        <v>2836.507230073812</v>
+      </c>
+      <c r="D11">
+        <v>3115.465230073812</v>
+      </c>
+      <c r="E11">
+        <v>294.358</v>
+      </c>
+      <c r="F11">
+        <v>310.158</v>
+      </c>
+      <c r="G11">
+        <v>31.2</v>
+      </c>
+      <c r="H11">
+        <v>3430.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>57.6</v>
+      </c>
+      <c r="K11">
+        <v>1.35</v>
+      </c>
+      <c r="L11">
+        <v>56.25</v>
+      </c>
+      <c r="M11">
+        <v>34.892775</v>
+      </c>
+      <c r="N11">
+        <v>21.357225</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>21.357225</v>
+      </c>
+      <c r="Q11">
+        <v>22.707225</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1131173558070876</v>
+      </c>
+      <c r="T11">
+        <v>1.098354551163455</v>
+      </c>
+      <c r="U11">
+        <v>0.1125</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.1125</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>1.612081584224814</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1222087937844497</v>
+      </c>
+      <c r="C12">
+        <v>2460.388683245796</v>
+      </c>
+      <c r="D12">
+        <v>2773.808683245796</v>
+      </c>
+      <c r="E12">
+        <v>328.8200000000001</v>
+      </c>
+      <c r="F12">
+        <v>344.6200000000001</v>
+      </c>
+      <c r="G12">
+        <v>31.2</v>
+      </c>
+      <c r="H12">
+        <v>3430.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>57.6</v>
+      </c>
+      <c r="K12">
+        <v>1.35</v>
+      </c>
+      <c r="L12">
+        <v>56.25</v>
+      </c>
+      <c r="M12">
+        <v>67.75229200000001</v>
+      </c>
+      <c r="N12">
+        <v>-11.50229200000001</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-11.50229200000001</v>
+      </c>
+      <c r="Q12">
+        <v>-10.15229200000001</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1139431042049441</v>
+      </c>
+      <c r="T12">
+        <v>1.110558490620827</v>
+      </c>
+      <c r="U12">
+        <v>0.1966</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.1966</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.8302302156803786</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1256787937844497</v>
+      </c>
+      <c r="C13">
+        <v>2315.138817627596</v>
+      </c>
+      <c r="D13">
+        <v>2663.020817627596</v>
+      </c>
+      <c r="E13">
+        <v>363.282</v>
+      </c>
+      <c r="F13">
+        <v>379.0820000000001</v>
+      </c>
+      <c r="G13">
+        <v>31.2</v>
+      </c>
+      <c r="H13">
+        <v>3430.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>57.6</v>
+      </c>
+      <c r="K13">
+        <v>1.35</v>
+      </c>
+      <c r="L13">
+        <v>56.25</v>
+      </c>
+      <c r="M13">
+        <v>81.04773160000001</v>
+      </c>
+      <c r="N13">
+        <v>-24.79773160000001</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-24.79773160000001</v>
+      </c>
+      <c r="Q13">
+        <v>-23.4477316</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1147874087465727</v>
+      </c>
+      <c r="T13">
+        <v>1.123036675908701</v>
+      </c>
+      <c r="U13">
+        <v>0.2138</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.2138</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.6940354639117376</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1274287937844497</v>
+      </c>
+      <c r="C14">
+        <v>2228.094736434182</v>
+      </c>
+      <c r="D14">
+        <v>2610.438736434182</v>
+      </c>
+      <c r="E14">
+        <v>397.744</v>
+      </c>
+      <c r="F14">
+        <v>413.544</v>
+      </c>
+      <c r="G14">
+        <v>31.2</v>
+      </c>
+      <c r="H14">
+        <v>3430.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>57.6</v>
+      </c>
+      <c r="K14">
+        <v>1.35</v>
+      </c>
+      <c r="L14">
+        <v>56.25</v>
+      </c>
+      <c r="M14">
+        <v>88.4157072</v>
+      </c>
+      <c r="N14">
+        <v>-32.1657072</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-32.1657072</v>
+      </c>
+      <c r="Q14">
+        <v>-30.8157072</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1156509020277837</v>
+      </c>
+      <c r="T14">
+        <v>1.135798456316755</v>
+      </c>
+      <c r="U14">
+        <v>0.2138</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.2138</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.6361991752524262</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1291787937844497</v>
+      </c>
+      <c r="C15">
+        <v>2143.086943583096</v>
+      </c>
+      <c r="D15">
+        <v>2559.892943583096</v>
+      </c>
+      <c r="E15">
+        <v>432.206</v>
+      </c>
+      <c r="F15">
+        <v>448.006</v>
+      </c>
+      <c r="G15">
+        <v>31.2</v>
+      </c>
+      <c r="H15">
+        <v>3430.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>57.6</v>
+      </c>
+      <c r="K15">
+        <v>1.35</v>
+      </c>
+      <c r="L15">
+        <v>56.25</v>
+      </c>
+      <c r="M15">
+        <v>95.78368280000001</v>
+      </c>
+      <c r="N15">
+        <v>-39.53368280000001</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-39.53368280000001</v>
+      </c>
+      <c r="Q15">
+        <v>-38.18368280000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1165342457292525</v>
+      </c>
+      <c r="T15">
+        <v>1.148853610987062</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.2138</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.5872607771560856</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1309287937844497</v>
+      </c>
+      <c r="C16">
+        <v>2059.999400283878</v>
+      </c>
+      <c r="D16">
+        <v>2511.267400283879</v>
+      </c>
+      <c r="E16">
+        <v>466.6680000000001</v>
+      </c>
+      <c r="F16">
+        <v>482.4680000000001</v>
+      </c>
+      <c r="G16">
+        <v>31.2</v>
+      </c>
+      <c r="H16">
+        <v>3430.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>57.6</v>
+      </c>
+      <c r="K16">
+        <v>1.35</v>
+      </c>
+      <c r="L16">
+        <v>56.25</v>
+      </c>
+      <c r="M16">
+        <v>103.1516584</v>
+      </c>
+      <c r="N16">
+        <v>-46.90165840000002</v>
+      </c>
+      <c r="O16">
+        <v>-0</v>
+      </c>
+      <c r="P16">
+        <v>-46.90165840000002</v>
+      </c>
+      <c r="Q16">
+        <v>-45.55165840000002</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1174381323074996</v>
+      </c>
+      <c r="T16">
+        <v>1.162212373905517</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.2138</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.5453135787877939</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1326787937844497</v>
+      </c>
+      <c r="C17">
+        <v>1978.724720089167</v>
+      </c>
+      <c r="D17">
+        <v>2464.454720089167</v>
+      </c>
+      <c r="E17">
+        <v>501.1300000000001</v>
+      </c>
+      <c r="F17">
+        <v>516.9300000000001</v>
+      </c>
+      <c r="G17">
+        <v>31.2</v>
+      </c>
+      <c r="H17">
+        <v>3430.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>57.6</v>
+      </c>
+      <c r="K17">
+        <v>1.35</v>
+      </c>
+      <c r="L17">
+        <v>56.25</v>
+      </c>
+      <c r="M17">
+        <v>110.519634</v>
+      </c>
+      <c r="N17">
+        <v>-54.26963400000001</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-54.26963400000001</v>
+      </c>
+      <c r="Q17">
+        <v>-52.91963400000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1183632868052349</v>
+      </c>
+      <c r="T17">
+        <v>1.175885460657346</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.2138</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.5089593402019409</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1384287937844497</v>
+      </c>
+      <c r="C18">
+        <v>1802.028591759044</v>
+      </c>
+      <c r="D18">
+        <v>2322.220591759044</v>
+      </c>
+      <c r="E18">
+        <v>535.5920000000001</v>
+      </c>
+      <c r="F18">
+        <v>551.3920000000001</v>
+      </c>
+      <c r="G18">
+        <v>31.2</v>
+      </c>
+      <c r="H18">
+        <v>3430.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>57.6</v>
+      </c>
+      <c r="K18">
+        <v>1.35</v>
+      </c>
+      <c r="L18">
+        <v>56.25</v>
+      </c>
+      <c r="M18">
+        <v>131.6724096</v>
+      </c>
+      <c r="N18">
+        <v>-75.42240960000001</v>
+      </c>
+      <c r="O18">
+        <v>-0</v>
+      </c>
+      <c r="P18">
+        <v>-75.42240960000001</v>
+      </c>
+      <c r="Q18">
+        <v>-74.07240960000001</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1193104687910115</v>
+      </c>
+      <c r="T18">
+        <v>1.189884097093743</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.2388</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.4271965567492736</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1404287937844497</v>
+      </c>
+      <c r="C19">
+        <v>1721.866539533996</v>
+      </c>
+      <c r="D19">
+        <v>2276.520539533996</v>
+      </c>
+      <c r="E19">
+        <v>570.0540000000001</v>
+      </c>
+      <c r="F19">
+        <v>585.854</v>
+      </c>
+      <c r="G19">
+        <v>31.2</v>
+      </c>
+      <c r="H19">
+        <v>3430.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>57.6</v>
+      </c>
+      <c r="K19">
+        <v>1.35</v>
+      </c>
+      <c r="L19">
+        <v>56.25</v>
+      </c>
+      <c r="M19">
+        <v>139.9019352</v>
+      </c>
+      <c r="N19">
+        <v>-83.65193520000003</v>
+      </c>
+      <c r="O19">
+        <v>-0</v>
+      </c>
+      <c r="P19">
+        <v>-83.65193520000003</v>
+      </c>
+      <c r="Q19">
+        <v>-82.30193520000003</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.120280474439096</v>
+      </c>
+      <c r="T19">
+        <v>1.204220050070776</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.2388</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.4020673475287281</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1424287937844497</v>
+      </c>
+      <c r="C20">
+        <v>1643.468477819927</v>
+      </c>
+      <c r="D20">
+        <v>2232.584477819927</v>
+      </c>
+      <c r="E20">
+        <v>604.5160000000001</v>
+      </c>
+      <c r="F20">
+        <v>620.316</v>
+      </c>
+      <c r="G20">
+        <v>31.2</v>
+      </c>
+      <c r="H20">
+        <v>3430.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>57.6</v>
+      </c>
+      <c r="K20">
+        <v>1.35</v>
+      </c>
+      <c r="L20">
+        <v>56.25</v>
+      </c>
+      <c r="M20">
+        <v>148.1314608</v>
+      </c>
+      <c r="N20">
+        <v>-91.88146080000001</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-91.88146080000001</v>
+      </c>
+      <c r="Q20">
+        <v>-90.53146080000002</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.121274138761524</v>
+      </c>
+      <c r="T20">
+        <v>1.218905660437493</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.2388</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.379730272666021</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1444287937844497</v>
+      </c>
+      <c r="C21">
+        <v>1566.734207204476</v>
+      </c>
+      <c r="D21">
+        <v>2190.312207204477</v>
+      </c>
+      <c r="E21">
+        <v>638.9780000000001</v>
+      </c>
+      <c r="F21">
+        <v>654.778</v>
+      </c>
+      <c r="G21">
+        <v>31.2</v>
+      </c>
+      <c r="H21">
+        <v>3430.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>57.6</v>
+      </c>
+      <c r="K21">
+        <v>1.35</v>
+      </c>
+      <c r="L21">
+        <v>56.25</v>
+      </c>
+      <c r="M21">
+        <v>156.3609864</v>
+      </c>
+      <c r="N21">
+        <v>-100.1109864</v>
+      </c>
+      <c r="O21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-100.1109864</v>
+      </c>
+      <c r="Q21">
+        <v>-98.76098640000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1222923380054934</v>
+      </c>
+      <c r="T21">
+        <v>1.233953878467585</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.2388</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.3597444688414936</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1464287937844497</v>
+      </c>
+      <c r="C22">
+        <v>1491.570976052689</v>
+      </c>
+      <c r="D22">
+        <v>2149.610976052689</v>
+      </c>
+      <c r="E22">
+        <v>673.4400000000002</v>
+      </c>
+      <c r="F22">
+        <v>689.2400000000001</v>
+      </c>
+      <c r="G22">
+        <v>31.2</v>
+      </c>
+      <c r="H22">
+        <v>3430.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>57.6</v>
+      </c>
+      <c r="K22">
+        <v>1.35</v>
+      </c>
+      <c r="L22">
+        <v>56.25</v>
+      </c>
+      <c r="M22">
+        <v>164.590512</v>
+      </c>
+      <c r="N22">
+        <v>-108.340512</v>
+      </c>
+      <c r="O22">
+        <v>-0</v>
+      </c>
+      <c r="P22">
+        <v>-108.340512</v>
+      </c>
+      <c r="Q22">
+        <v>-106.9905120000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1233359922305621</v>
+      </c>
+      <c r="T22">
+        <v>1.24937830194843</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.2388</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.3417572453994188</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1484287937844497</v>
+      </c>
+      <c r="C23">
+        <v>1417.892801143765</v>
+      </c>
+      <c r="D23">
+        <v>2110.394801143766</v>
+      </c>
+      <c r="E23">
+        <v>707.902</v>
+      </c>
+      <c r="F23">
+        <v>723.702</v>
+      </c>
+      <c r="G23">
+        <v>31.2</v>
+      </c>
+      <c r="H23">
+        <v>3430.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>57.6</v>
+      </c>
+      <c r="K23">
+        <v>1.35</v>
+      </c>
+      <c r="L23">
+        <v>56.25</v>
+      </c>
+      <c r="M23">
+        <v>172.8200376</v>
+      </c>
+      <c r="N23">
+        <v>-116.5700376</v>
+      </c>
+      <c r="O23">
+        <v>-0</v>
+      </c>
+      <c r="P23">
+        <v>-116.5700376</v>
+      </c>
+      <c r="Q23">
+        <v>-115.2200376</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1244060680815819</v>
+      </c>
+      <c r="T23">
+        <v>1.265193217162967</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.2388</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3254830908565894</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1504287937844497</v>
+      </c>
+      <c r="C24">
+        <v>1345.619861338774</v>
+      </c>
+      <c r="D24">
+        <v>2072.583861338775</v>
+      </c>
+      <c r="E24">
+        <v>742.3640000000001</v>
+      </c>
+      <c r="F24">
+        <v>758.1640000000001</v>
+      </c>
+      <c r="G24">
+        <v>31.2</v>
+      </c>
+      <c r="H24">
+        <v>3430.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>57.6</v>
+      </c>
+      <c r="K24">
+        <v>1.35</v>
+      </c>
+      <c r="L24">
+        <v>56.25</v>
+      </c>
+      <c r="M24">
+        <v>181.0495632</v>
+      </c>
+      <c r="N24">
+        <v>-124.7995632</v>
+      </c>
+      <c r="O24">
+        <v>-0</v>
+      </c>
+      <c r="P24">
+        <v>-124.7995632</v>
+      </c>
+      <c r="Q24">
+        <v>-123.4495632</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1255035817749355</v>
+      </c>
+      <c r="T24">
+        <v>1.281413643024031</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.2388</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3106884049085626</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1524287937844497</v>
+      </c>
+      <c r="C25">
+        <v>1274.677955281329</v>
+      </c>
+      <c r="D25">
+        <v>2036.103955281329</v>
+      </c>
+      <c r="E25">
+        <v>776.8260000000001</v>
+      </c>
+      <c r="F25">
+        <v>792.6260000000001</v>
+      </c>
+      <c r="G25">
+        <v>31.2</v>
+      </c>
+      <c r="H25">
+        <v>3430.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>57.6</v>
+      </c>
+      <c r="K25">
+        <v>1.35</v>
+      </c>
+      <c r="L25">
+        <v>56.25</v>
+      </c>
+      <c r="M25">
+        <v>189.2790888</v>
+      </c>
+      <c r="N25">
+        <v>-133.0290888</v>
+      </c>
+      <c r="O25">
+        <v>-0</v>
+      </c>
+      <c r="P25">
+        <v>-133.0290888</v>
+      </c>
+      <c r="Q25">
+        <v>-131.6790888</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1266296023174671</v>
+      </c>
+      <c r="T25">
+        <v>1.29805537864772</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.2388</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.2971802133907989</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1544287937844497</v>
+      </c>
+      <c r="C26">
+        <v>1204.998015378282</v>
+      </c>
+      <c r="D26">
+        <v>2000.886015378282</v>
+      </c>
+      <c r="E26">
+        <v>811.2880000000001</v>
+      </c>
+      <c r="F26">
+        <v>827.0880000000001</v>
+      </c>
+      <c r="G26">
+        <v>31.2</v>
+      </c>
+      <c r="H26">
+        <v>3430.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>57.6</v>
+      </c>
+      <c r="K26">
+        <v>1.35</v>
+      </c>
+      <c r="L26">
+        <v>56.25</v>
+      </c>
+      <c r="M26">
+        <v>197.5086144</v>
+      </c>
+      <c r="N26">
+        <v>-141.2586144</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-141.2586144</v>
+      </c>
+      <c r="Q26">
+        <v>-139.9086144</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1277852549795391</v>
+      </c>
+      <c r="T26">
+        <v>1.315135054682558</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.2388</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.2847977044995157</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1564287937844497</v>
+      </c>
+      <c r="C27">
+        <v>1136.51567136209</v>
+      </c>
+      <c r="D27">
+        <v>1966.865671362091</v>
+      </c>
+      <c r="E27">
+        <v>845.7500000000001</v>
+      </c>
+      <c r="F27">
+        <v>861.5500000000001</v>
+      </c>
+      <c r="G27">
+        <v>31.2</v>
+      </c>
+      <c r="H27">
+        <v>3430.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>57.6</v>
+      </c>
+      <c r="K27">
+        <v>1.35</v>
+      </c>
+      <c r="L27">
+        <v>56.25</v>
+      </c>
+      <c r="M27">
+        <v>205.73814</v>
+      </c>
+      <c r="N27">
+        <v>-149.48814</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-149.48814</v>
+      </c>
+      <c r="Q27">
+        <v>-148.13814</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1289717250459329</v>
+      </c>
+      <c r="T27">
+        <v>1.332670188744992</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.2388</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.2734057963195351</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1584287937844497</v>
+      </c>
+      <c r="C28">
+        <v>1069.170857632379</v>
+      </c>
+      <c r="D28">
+        <v>1933.982857632378</v>
+      </c>
+      <c r="E28">
+        <v>880.2120000000001</v>
+      </c>
+      <c r="F28">
+        <v>896.0120000000001</v>
+      </c>
+      <c r="G28">
+        <v>31.2</v>
+      </c>
+      <c r="H28">
+        <v>3430.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>57.6</v>
+      </c>
+      <c r="K28">
+        <v>1.35</v>
+      </c>
+      <c r="L28">
+        <v>56.25</v>
+      </c>
+      <c r="M28">
+        <v>213.9676656</v>
+      </c>
+      <c r="N28">
+        <v>-157.7176656</v>
+      </c>
+      <c r="O28">
+        <v>-0</v>
+      </c>
+      <c r="P28">
+        <v>-157.7176656</v>
+      </c>
+      <c r="Q28">
+        <v>-156.3676656</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.130190261870878</v>
+      </c>
+      <c r="T28">
+        <v>1.350679245349654</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.2388</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.2628901887687837</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1604287937844497</v>
+      </c>
+      <c r="C29">
+        <v>1002.907459337501</v>
+      </c>
+      <c r="D29">
+        <v>1902.181459337501</v>
+      </c>
+      <c r="E29">
+        <v>914.6740000000002</v>
+      </c>
+      <c r="F29">
+        <v>930.4740000000002</v>
+      </c>
+      <c r="G29">
+        <v>31.2</v>
+      </c>
+      <c r="H29">
+        <v>3430.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>57.6</v>
+      </c>
+      <c r="K29">
+        <v>1.35</v>
+      </c>
+      <c r="L29">
+        <v>56.25</v>
+      </c>
+      <c r="M29">
+        <v>222.1971912</v>
+      </c>
+      <c r="N29">
+        <v>-165.9471912</v>
+      </c>
+      <c r="O29">
+        <v>-0</v>
+      </c>
+      <c r="P29">
+        <v>-165.9471912</v>
+      </c>
+      <c r="Q29">
+        <v>-164.5971912000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1314421832663694</v>
+      </c>
+      <c r="T29">
+        <v>1.369181700765403</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.2388</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2531535151106806</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1624287937844497</v>
+      </c>
+      <c r="C30">
+        <v>937.6729928091293</v>
+      </c>
+      <c r="D30">
+        <v>1871.408992809129</v>
+      </c>
+      <c r="E30">
+        <v>949.1360000000002</v>
+      </c>
+      <c r="F30">
+        <v>964.9360000000001</v>
+      </c>
+      <c r="G30">
+        <v>31.2</v>
+      </c>
+      <c r="H30">
+        <v>3430.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>57.6</v>
+      </c>
+      <c r="K30">
+        <v>1.35</v>
+      </c>
+      <c r="L30">
+        <v>56.25</v>
+      </c>
+      <c r="M30">
+        <v>230.4267168</v>
+      </c>
+      <c r="N30">
+        <v>-174.1767168</v>
+      </c>
+      <c r="O30">
+        <v>-0</v>
+      </c>
+      <c r="P30">
+        <v>-174.1767168</v>
+      </c>
+      <c r="Q30">
+        <v>-172.8267168</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1327288802561801</v>
+      </c>
+      <c r="T30">
+        <v>1.388198113276034</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.2388</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2441123181424421</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1644287937844497</v>
+      </c>
+      <c r="C31">
+        <v>873.4183165215576</v>
+      </c>
+      <c r="D31">
+        <v>1841.616316521558</v>
+      </c>
+      <c r="E31">
+        <v>983.5980000000001</v>
+      </c>
+      <c r="F31">
+        <v>999.398</v>
+      </c>
+      <c r="G31">
+        <v>31.2</v>
+      </c>
+      <c r="H31">
+        <v>3430.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>57.6</v>
+      </c>
+      <c r="K31">
+        <v>1.35</v>
+      </c>
+      <c r="L31">
+        <v>56.25</v>
+      </c>
+      <c r="M31">
+        <v>238.6562424</v>
+      </c>
+      <c r="N31">
+        <v>-182.4062424</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-182.4062424</v>
+      </c>
+      <c r="Q31">
+        <v>-181.0562424</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1340518222316193</v>
+      </c>
+      <c r="T31">
+        <v>1.407750199378513</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.2388</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2356946519995992</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1664287937844497</v>
+      </c>
+      <c r="C32">
+        <v>810.0973692273933</v>
+      </c>
+      <c r="D32">
+        <v>1812.757369227393</v>
+      </c>
+      <c r="E32">
+        <v>1018.06</v>
+      </c>
+      <c r="F32">
+        <v>1033.86</v>
+      </c>
+      <c r="G32">
+        <v>31.2</v>
+      </c>
+      <c r="H32">
+        <v>3430.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>57.6</v>
+      </c>
+      <c r="K32">
+        <v>1.35</v>
+      </c>
+      <c r="L32">
+        <v>56.25</v>
+      </c>
+      <c r="M32">
+        <v>246.885768</v>
+      </c>
+      <c r="N32">
+        <v>-190.635768</v>
+      </c>
+      <c r="O32">
+        <v>-0</v>
+      </c>
+      <c r="P32">
+        <v>-190.635768</v>
+      </c>
+      <c r="Q32">
+        <v>-189.285768</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1354125625492139</v>
+      </c>
+      <c r="T32">
+        <v>1.427860916512492</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.2388</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2278381635996125</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1684287937844497</v>
+      </c>
+      <c r="C33">
+        <v>747.6669323345579</v>
+      </c>
+      <c r="D33">
+        <v>1784.788932334558</v>
+      </c>
+      <c r="E33">
+        <v>1052.522</v>
+      </c>
+      <c r="F33">
+        <v>1068.322</v>
+      </c>
+      <c r="G33">
+        <v>31.2</v>
+      </c>
+      <c r="H33">
+        <v>3430.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>57.6</v>
+      </c>
+      <c r="K33">
+        <v>1.35</v>
+      </c>
+      <c r="L33">
+        <v>56.25</v>
+      </c>
+      <c r="M33">
+        <v>255.1152936</v>
+      </c>
+      <c r="N33">
+        <v>-198.8652936</v>
+      </c>
+      <c r="O33">
+        <v>-0</v>
+      </c>
+      <c r="P33">
+        <v>-198.8652936</v>
+      </c>
+      <c r="Q33">
+        <v>-197.5152936</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1368127446151445</v>
+      </c>
+      <c r="T33">
+        <v>1.448554552983687</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.2388</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2204885454189799</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1704287937844497</v>
+      </c>
+      <c r="C34">
+        <v>686.0864139462897</v>
+      </c>
+      <c r="D34">
+        <v>1757.67041394629</v>
+      </c>
+      <c r="E34">
+        <v>1086.984</v>
+      </c>
+      <c r="F34">
+        <v>1102.784</v>
+      </c>
+      <c r="G34">
+        <v>31.2</v>
+      </c>
+      <c r="H34">
+        <v>3430.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>57.6</v>
+      </c>
+      <c r="K34">
+        <v>1.35</v>
+      </c>
+      <c r="L34">
+        <v>56.25</v>
+      </c>
+      <c r="M34">
+        <v>263.3448192</v>
+      </c>
+      <c r="N34">
+        <v>-207.0948192</v>
+      </c>
+      <c r="O34">
+        <v>-0</v>
+      </c>
+      <c r="P34">
+        <v>-207.0948192</v>
+      </c>
+      <c r="Q34">
+        <v>-205.7448192</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1382541085065437</v>
+      </c>
+      <c r="T34">
+        <v>1.469856825821683</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.2388</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2135982783746367</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1724287937844497</v>
+      </c>
+      <c r="C35">
+        <v>625.3176522945832</v>
+      </c>
+      <c r="D35">
+        <v>1731.363652294583</v>
+      </c>
+      <c r="E35">
+        <v>1121.446</v>
+      </c>
+      <c r="F35">
+        <v>1137.246</v>
+      </c>
+      <c r="G35">
+        <v>31.2</v>
+      </c>
+      <c r="H35">
+        <v>3430.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>57.6</v>
+      </c>
+      <c r="K35">
+        <v>1.35</v>
+      </c>
+      <c r="L35">
+        <v>56.25</v>
+      </c>
+      <c r="M35">
+        <v>271.5743448000001</v>
+      </c>
+      <c r="N35">
+        <v>-215.3243448000001</v>
+      </c>
+      <c r="O35">
+        <v>-0</v>
+      </c>
+      <c r="P35">
+        <v>-215.3243448000001</v>
+      </c>
+      <c r="Q35">
+        <v>-213.9743448000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1397384981857458</v>
+      </c>
+      <c r="T35">
+        <v>1.491794987401111</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.2388</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2071256032723751</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1744287937844497</v>
+      </c>
+      <c r="C36">
+        <v>565.3247365651962</v>
+      </c>
+      <c r="D36">
+        <v>1705.832736565196</v>
+      </c>
+      <c r="E36">
+        <v>1155.908</v>
+      </c>
+      <c r="F36">
+        <v>1171.708</v>
+      </c>
+      <c r="G36">
+        <v>31.2</v>
+      </c>
+      <c r="H36">
+        <v>3430.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>57.6</v>
+      </c>
+      <c r="K36">
+        <v>1.35</v>
+      </c>
+      <c r="L36">
+        <v>56.25</v>
+      </c>
+      <c r="M36">
+        <v>279.8038704000001</v>
+      </c>
+      <c r="N36">
+        <v>-223.5538704000001</v>
+      </c>
+      <c r="O36">
+        <v>-0</v>
+      </c>
+      <c r="P36">
+        <v>-223.5538704000001</v>
+      </c>
+      <c r="Q36">
+        <v>-222.2038704000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1412678693703783</v>
+      </c>
+      <c r="T36">
+        <v>1.514397941755673</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.2388</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.201033673764364</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1764287937844497</v>
+      </c>
+      <c r="C37">
+        <v>506.0738433451218</v>
+      </c>
+      <c r="D37">
+        <v>1681.043843345122</v>
+      </c>
+      <c r="E37">
+        <v>1190.37</v>
+      </c>
+      <c r="F37">
+        <v>1206.17</v>
+      </c>
+      <c r="G37">
+        <v>31.2</v>
+      </c>
+      <c r="H37">
+        <v>3430.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>57.6</v>
+      </c>
+      <c r="K37">
+        <v>1.35</v>
+      </c>
+      <c r="L37">
+        <v>56.25</v>
+      </c>
+      <c r="M37">
+        <v>288.0333960000001</v>
+      </c>
+      <c r="N37">
+        <v>-231.7833960000001</v>
+      </c>
+      <c r="O37">
+        <v>-0</v>
+      </c>
+      <c r="P37">
+        <v>-231.7833960000001</v>
+      </c>
+      <c r="Q37">
+        <v>-230.4333960000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1428442981299226</v>
+      </c>
+      <c r="T37">
+        <v>1.537696371628837</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.2388</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1952898545139536</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1784287937844497</v>
+      </c>
+      <c r="C38">
+        <v>447.5330871261115</v>
+      </c>
+      <c r="D38">
+        <v>1656.965087126111</v>
+      </c>
+      <c r="E38">
+        <v>1224.832</v>
+      </c>
+      <c r="F38">
+        <v>1240.632</v>
+      </c>
+      <c r="G38">
+        <v>31.2</v>
+      </c>
+      <c r="H38">
+        <v>3430.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>57.6</v>
+      </c>
+      <c r="K38">
+        <v>1.35</v>
+      </c>
+      <c r="L38">
+        <v>56.25</v>
+      </c>
+      <c r="M38">
+        <v>296.2629216</v>
+      </c>
+      <c r="N38">
+        <v>-240.0129216</v>
+      </c>
+      <c r="O38">
+        <v>-0</v>
+      </c>
+      <c r="P38">
+        <v>-240.0129216</v>
+      </c>
+      <c r="Q38">
+        <v>-238.6629216</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1444699902882026</v>
+      </c>
+      <c r="T38">
+        <v>1.561722877435538</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.2388</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1898651363330105</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1804287937844497</v>
+      </c>
+      <c r="C39">
+        <v>389.6723834748195</v>
+      </c>
+      <c r="D39">
+        <v>1633.56638347482</v>
+      </c>
+      <c r="E39">
+        <v>1259.294</v>
+      </c>
+      <c r="F39">
+        <v>1275.094</v>
+      </c>
+      <c r="G39">
+        <v>31.2</v>
+      </c>
+      <c r="H39">
+        <v>3430.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>57.6</v>
+      </c>
+      <c r="K39">
+        <v>1.35</v>
+      </c>
+      <c r="L39">
+        <v>56.25</v>
+      </c>
+      <c r="M39">
+        <v>304.4924472</v>
+      </c>
+      <c r="N39">
+        <v>-248.2424472</v>
+      </c>
+      <c r="O39">
+        <v>-0</v>
+      </c>
+      <c r="P39">
+        <v>-248.2424472</v>
+      </c>
+      <c r="Q39">
+        <v>-246.8924472</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1461472917213487</v>
+      </c>
+      <c r="T39">
+        <v>1.586512129458324</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.2388</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1847336461618481</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1824287937844497</v>
+      </c>
+      <c r="C40">
+        <v>332.4633236349057</v>
+      </c>
+      <c r="D40">
+        <v>1610.819323634906</v>
+      </c>
+      <c r="E40">
+        <v>1293.756</v>
+      </c>
+      <c r="F40">
+        <v>1309.556</v>
+      </c>
+      <c r="G40">
+        <v>31.2</v>
+      </c>
+      <c r="H40">
+        <v>3430.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>57.6</v>
+      </c>
+      <c r="K40">
+        <v>1.35</v>
+      </c>
+      <c r="L40">
+        <v>56.25</v>
+      </c>
+      <c r="M40">
+        <v>312.7219728</v>
+      </c>
+      <c r="N40">
+        <v>-256.4719728</v>
+      </c>
+      <c r="O40">
+        <v>-0</v>
+      </c>
+      <c r="P40">
+        <v>-256.4719728</v>
+      </c>
+      <c r="Q40">
+        <v>-255.1219728</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1478786996523382</v>
+      </c>
+      <c r="T40">
+        <v>1.612101034772168</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.2388</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1798722344207467</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1844287937844497</v>
+      </c>
+      <c r="C41">
+        <v>275.8790594620775</v>
+      </c>
+      <c r="D41">
+        <v>1588.697059462078</v>
+      </c>
+      <c r="E41">
+        <v>1328.218</v>
+      </c>
+      <c r="F41">
+        <v>1344.018</v>
+      </c>
+      <c r="G41">
+        <v>31.2</v>
+      </c>
+      <c r="H41">
+        <v>3430.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>57.6</v>
+      </c>
+      <c r="K41">
+        <v>1.35</v>
+      </c>
+      <c r="L41">
+        <v>56.25</v>
+      </c>
+      <c r="M41">
+        <v>320.9514984000001</v>
+      </c>
+      <c r="N41">
+        <v>-264.7014984000001</v>
+      </c>
+      <c r="O41">
+        <v>-0</v>
+      </c>
+      <c r="P41">
+        <v>-264.7014984000001</v>
+      </c>
+      <c r="Q41">
+        <v>-263.3514984000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1496668750564749</v>
+      </c>
+      <c r="T41">
+        <v>1.638528920588105</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.2388</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1752601258458558</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1864287937844497</v>
+      </c>
+      <c r="C42">
+        <v>219.8941977121981</v>
+      </c>
+      <c r="D42">
+        <v>1567.174197712198</v>
+      </c>
+      <c r="E42">
+        <v>1362.68</v>
+      </c>
+      <c r="F42">
+        <v>1378.48</v>
+      </c>
+      <c r="G42">
+        <v>31.2</v>
+      </c>
+      <c r="H42">
+        <v>3430.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>57.6</v>
+      </c>
+      <c r="K42">
+        <v>1.35</v>
+      </c>
+      <c r="L42">
+        <v>56.25</v>
+      </c>
+      <c r="M42">
+        <v>329.1810240000001</v>
+      </c>
+      <c r="N42">
+        <v>-272.9310240000001</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-272.9310240000001</v>
+      </c>
+      <c r="Q42">
+        <v>-271.5810240000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1515146563074161</v>
+      </c>
+      <c r="T42">
+        <v>1.66583773593124</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.2388</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1708786226997094</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1884287937844497</v>
+      </c>
+      <c r="C43">
+        <v>164.4847028073098</v>
+      </c>
+      <c r="D43">
+        <v>1546.22670280731</v>
+      </c>
+      <c r="E43">
+        <v>1397.142</v>
+      </c>
+      <c r="F43">
+        <v>1412.942</v>
+      </c>
+      <c r="G43">
+        <v>31.2</v>
+      </c>
+      <c r="H43">
+        <v>3430.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>57.6</v>
+      </c>
+      <c r="K43">
+        <v>1.35</v>
+      </c>
+      <c r="L43">
+        <v>56.25</v>
+      </c>
+      <c r="M43">
+        <v>337.4105496000001</v>
+      </c>
+      <c r="N43">
+        <v>-281.1605496000001</v>
+      </c>
+      <c r="O43">
+        <v>-0</v>
+      </c>
+      <c r="P43">
+        <v>-281.1605496000001</v>
+      </c>
+      <c r="Q43">
+        <v>-279.8105496000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1534250742109317</v>
+      </c>
+      <c r="T43">
+        <v>1.69407227382838</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.2388</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1667108514143506</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1904287937844497</v>
+      </c>
+      <c r="C44">
+        <v>109.6278072968255</v>
+      </c>
+      <c r="D44">
+        <v>1525.831807296825</v>
+      </c>
+      <c r="E44">
+        <v>1431.604</v>
+      </c>
+      <c r="F44">
+        <v>1447.404</v>
+      </c>
+      <c r="G44">
+        <v>31.2</v>
+      </c>
+      <c r="H44">
+        <v>3430.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>57.6</v>
+      </c>
+      <c r="K44">
+        <v>1.35</v>
+      </c>
+      <c r="L44">
+        <v>56.25</v>
+      </c>
+      <c r="M44">
+        <v>345.6400752</v>
+      </c>
+      <c r="N44">
+        <v>-289.3900752</v>
+      </c>
+      <c r="O44">
+        <v>-0</v>
+      </c>
+      <c r="P44">
+        <v>-289.3900752</v>
+      </c>
+      <c r="Q44">
+        <v>-288.0400752</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1554013685938788</v>
+      </c>
+      <c r="T44">
+        <v>1.723280416480593</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.2388</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1627415454282947</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1924287937844497</v>
+      </c>
+      <c r="C45">
+        <v>55.30192931262877</v>
+      </c>
+      <c r="D45">
+        <v>1505.967929312629</v>
+      </c>
+      <c r="E45">
+        <v>1466.066</v>
+      </c>
+      <c r="F45">
+        <v>1481.866</v>
+      </c>
+      <c r="G45">
+        <v>31.2</v>
+      </c>
+      <c r="H45">
+        <v>3430.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>57.6</v>
+      </c>
+      <c r="K45">
+        <v>1.35</v>
+      </c>
+      <c r="L45">
+        <v>56.25</v>
+      </c>
+      <c r="M45">
+        <v>353.8696008</v>
+      </c>
+      <c r="N45">
+        <v>-297.6196008</v>
+      </c>
+      <c r="O45">
+        <v>-0</v>
+      </c>
+      <c r="P45">
+        <v>-297.6196008</v>
+      </c>
+      <c r="Q45">
+        <v>-296.2696008</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1574470066393854</v>
+      </c>
+      <c r="T45">
+        <v>1.753513406243411</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.2388</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1589568583253111</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1944287937844497</v>
+      </c>
+      <c r="C46">
+        <v>1.48659638892218</v>
+      </c>
+      <c r="D46">
+        <v>1486.614596388922</v>
+      </c>
+      <c r="E46">
+        <v>1500.528</v>
+      </c>
+      <c r="F46">
+        <v>1516.328</v>
+      </c>
+      <c r="G46">
+        <v>31.2</v>
+      </c>
+      <c r="H46">
+        <v>3430.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>57.6</v>
+      </c>
+      <c r="K46">
+        <v>1.35</v>
+      </c>
+      <c r="L46">
+        <v>56.25</v>
+      </c>
+      <c r="M46">
+        <v>362.0991264</v>
+      </c>
+      <c r="N46">
+        <v>-305.8491264</v>
+      </c>
+      <c r="O46">
+        <v>-0</v>
+      </c>
+      <c r="P46">
+        <v>-305.8491264</v>
+      </c>
+      <c r="Q46">
+        <v>-304.4991264</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1595657031865173</v>
+      </c>
+      <c r="T46">
+        <v>1.784826145640615</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.2388</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1553442024542813</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1964287937844497</v>
+      </c>
+      <c r="C47">
+        <v>-51.83762491845914</v>
+      </c>
+      <c r="D47">
+        <v>1467.752375081541</v>
+      </c>
+      <c r="E47">
+        <v>1534.99</v>
+      </c>
+      <c r="F47">
+        <v>1550.79</v>
+      </c>
+      <c r="G47">
+        <v>31.2</v>
+      </c>
+      <c r="H47">
+        <v>3430.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>57.6</v>
+      </c>
+      <c r="K47">
+        <v>1.35</v>
+      </c>
+      <c r="L47">
+        <v>56.25</v>
+      </c>
+      <c r="M47">
+        <v>370.3286520000001</v>
+      </c>
+      <c r="N47">
+        <v>-314.0786520000001</v>
+      </c>
+      <c r="O47">
+        <v>-0</v>
+      </c>
+      <c r="P47">
+        <v>-314.0786520000001</v>
+      </c>
+      <c r="Q47">
+        <v>-312.7286520000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.161761443244454</v>
+      </c>
+      <c r="T47">
+        <v>1.817277530106808</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.2388</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1518921090664084</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1984287937844497</v>
+      </c>
+      <c r="C48">
+        <v>-104.6891941219135</v>
+      </c>
+      <c r="D48">
+        <v>1449.362805878087</v>
+      </c>
+      <c r="E48">
+        <v>1569.452</v>
+      </c>
+      <c r="F48">
+        <v>1585.252</v>
+      </c>
+      <c r="G48">
+        <v>31.2</v>
+      </c>
+      <c r="H48">
+        <v>3430.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>57.6</v>
+      </c>
+      <c r="K48">
+        <v>1.35</v>
+      </c>
+      <c r="L48">
+        <v>56.25</v>
+      </c>
+      <c r="M48">
+        <v>378.5581776000001</v>
+      </c>
+      <c r="N48">
+        <v>-322.3081776000001</v>
+      </c>
+      <c r="O48">
+        <v>-0</v>
+      </c>
+      <c r="P48">
+        <v>-322.3081776000001</v>
+      </c>
+      <c r="Q48">
+        <v>-320.9581776000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1640385070082402</v>
+      </c>
+      <c r="T48">
+        <v>1.850930817701378</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.2388</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1485901066953995</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2004287937844497</v>
+      </c>
+      <c r="C49">
+        <v>-157.0856570593896</v>
+      </c>
+      <c r="D49">
+        <v>1431.42834294061</v>
+      </c>
+      <c r="E49">
+        <v>1603.914</v>
+      </c>
+      <c r="F49">
+        <v>1619.714</v>
+      </c>
+      <c r="G49">
+        <v>31.2</v>
+      </c>
+      <c r="H49">
+        <v>3430.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>57.6</v>
+      </c>
+      <c r="K49">
+        <v>1.35</v>
+      </c>
+      <c r="L49">
+        <v>56.25</v>
+      </c>
+      <c r="M49">
+        <v>386.7877032000001</v>
+      </c>
+      <c r="N49">
+        <v>-330.5377032000001</v>
+      </c>
+      <c r="O49">
+        <v>-0</v>
+      </c>
+      <c r="P49">
+        <v>-330.5377032000001</v>
+      </c>
+      <c r="Q49">
+        <v>-329.1877032</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1664014977065089</v>
+      </c>
+      <c r="T49">
+        <v>1.885854040676876</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.2388</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1454286150635825</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2024287937844497</v>
+      </c>
+      <c r="C50">
+        <v>-209.0437017326296</v>
+      </c>
+      <c r="D50">
+        <v>1413.93229826737</v>
+      </c>
+      <c r="E50">
+        <v>1638.376</v>
+      </c>
+      <c r="F50">
+        <v>1654.176</v>
+      </c>
+      <c r="G50">
+        <v>31.2</v>
+      </c>
+      <c r="H50">
+        <v>3430.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>57.6</v>
+      </c>
+      <c r="K50">
+        <v>1.35</v>
+      </c>
+      <c r="L50">
+        <v>56.25</v>
+      </c>
+      <c r="M50">
+        <v>395.0172288000001</v>
+      </c>
+      <c r="N50">
+        <v>-338.7672288000001</v>
+      </c>
+      <c r="O50">
+        <v>-0</v>
+      </c>
+      <c r="P50">
+        <v>-338.7672288000001</v>
+      </c>
+      <c r="Q50">
+        <v>-337.4172288</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1688553726624032</v>
+      </c>
+      <c r="T50">
+        <v>1.922120464536046</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.2388</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1423988522497579</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2044287937844497</v>
+      </c>
+      <c r="C51">
+        <v>-260.5792100998701</v>
+      </c>
+      <c r="D51">
+        <v>1396.85878990013</v>
+      </c>
+      <c r="E51">
+        <v>1672.838</v>
+      </c>
+      <c r="F51">
+        <v>1688.638</v>
+      </c>
+      <c r="G51">
+        <v>31.2</v>
+      </c>
+      <c r="H51">
+        <v>3430.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>57.6</v>
+      </c>
+      <c r="K51">
+        <v>1.35</v>
+      </c>
+      <c r="L51">
+        <v>56.25</v>
+      </c>
+      <c r="M51">
+        <v>403.2467544</v>
+      </c>
+      <c r="N51">
+        <v>-346.9967544</v>
+      </c>
+      <c r="O51">
+        <v>-0</v>
+      </c>
+      <c r="P51">
+        <v>-346.9967544</v>
+      </c>
+      <c r="Q51">
+        <v>-345.6467544</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1714054780087249</v>
+      </c>
+      <c r="T51">
+        <v>1.959809101095577</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.2388</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1394927532242526</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2064287937844497</v>
+      </c>
+      <c r="C52">
+        <v>-311.7073061608646</v>
+      </c>
+      <c r="D52">
+        <v>1380.192693839135</v>
+      </c>
+      <c r="E52">
+        <v>1707.3</v>
+      </c>
+      <c r="F52">
+        <v>1723.1</v>
+      </c>
+      <c r="G52">
+        <v>31.2</v>
+      </c>
+      <c r="H52">
+        <v>3430.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>57.6</v>
+      </c>
+      <c r="K52">
+        <v>1.35</v>
+      </c>
+      <c r="L52">
+        <v>56.25</v>
+      </c>
+      <c r="M52">
+        <v>411.47628</v>
+      </c>
+      <c r="N52">
+        <v>-355.22628</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-355.22628</v>
+      </c>
+      <c r="Q52">
+        <v>-353.87628</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1740575875688994</v>
+      </c>
+      <c r="T52">
+        <v>1.999005283117488</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.2388</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1367028981597675</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2084287937844497</v>
+      </c>
+      <c r="C53">
+        <v>-362.4424006402485</v>
+      </c>
+      <c r="D53">
+        <v>1363.919599359752</v>
+      </c>
+      <c r="E53">
+        <v>1741.762</v>
+      </c>
+      <c r="F53">
+        <v>1757.562</v>
+      </c>
+      <c r="G53">
+        <v>31.2</v>
+      </c>
+      <c r="H53">
+        <v>3430.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>57.6</v>
+      </c>
+      <c r="K53">
+        <v>1.35</v>
+      </c>
+      <c r="L53">
+        <v>56.25</v>
+      </c>
+      <c r="M53">
+        <v>419.7058056000001</v>
+      </c>
+      <c r="N53">
+        <v>-363.4558056000001</v>
+      </c>
+      <c r="O53">
+        <v>-0</v>
+      </c>
+      <c r="P53">
+        <v>-363.4558056000001</v>
+      </c>
+      <c r="Q53">
+        <v>-362.1058056000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1768179464988769</v>
+      </c>
+      <c r="T53">
+        <v>2.03980130930356</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.2388</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1340224491762427</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2104287937844497</v>
+      </c>
+      <c r="C54">
+        <v>-412.7982325467142</v>
+      </c>
+      <c r="D54">
+        <v>1348.025767453286</v>
+      </c>
+      <c r="E54">
+        <v>1776.224</v>
+      </c>
+      <c r="F54">
+        <v>1792.024</v>
+      </c>
+      <c r="G54">
+        <v>31.2</v>
+      </c>
+      <c r="H54">
+        <v>3430.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>57.6</v>
+      </c>
+      <c r="K54">
+        <v>1.35</v>
+      </c>
+      <c r="L54">
+        <v>56.25</v>
+      </c>
+      <c r="M54">
+        <v>427.9353312000001</v>
+      </c>
+      <c r="N54">
+        <v>-371.6853312000001</v>
+      </c>
+      <c r="O54">
+        <v>-0</v>
+      </c>
+      <c r="P54">
+        <v>-371.6853312000001</v>
+      </c>
+      <c r="Q54">
+        <v>-370.3353312</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1796933203842702</v>
+      </c>
+      <c r="T54">
+        <v>2.08229716991405</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.2388</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1314450943843919</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2124287937844497</v>
+      </c>
+      <c r="C55">
+        <v>-462.7879078599092</v>
+      </c>
+      <c r="D55">
+        <v>1332.498092140091</v>
+      </c>
+      <c r="E55">
+        <v>1810.686</v>
+      </c>
+      <c r="F55">
+        <v>1826.486</v>
+      </c>
+      <c r="G55">
+        <v>31.2</v>
+      </c>
+      <c r="H55">
+        <v>3430.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>57.6</v>
+      </c>
+      <c r="K55">
+        <v>1.35</v>
+      </c>
+      <c r="L55">
+        <v>56.25</v>
+      </c>
+      <c r="M55">
+        <v>436.1648568000001</v>
+      </c>
+      <c r="N55">
+        <v>-379.9148568000001</v>
+      </c>
+      <c r="O55">
+        <v>-0</v>
+      </c>
+      <c r="P55">
+        <v>-379.9148568000001</v>
+      </c>
+      <c r="Q55">
+        <v>-378.5648568000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1826910506052121</v>
+      </c>
+      <c r="T55">
+        <v>2.126601365018605</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.2388</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1289649982639316</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2144287937844497</v>
+      </c>
+      <c r="C56">
+        <v>-512.4239355740146</v>
+      </c>
+      <c r="D56">
+        <v>1317.324064425986</v>
+      </c>
+      <c r="E56">
+        <v>1845.148</v>
+      </c>
+      <c r="F56">
+        <v>1860.948</v>
+      </c>
+      <c r="G56">
+        <v>31.2</v>
+      </c>
+      <c r="H56">
+        <v>3430.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>57.6</v>
+      </c>
+      <c r="K56">
+        <v>1.35</v>
+      </c>
+      <c r="L56">
+        <v>56.25</v>
+      </c>
+      <c r="M56">
+        <v>444.3943824000001</v>
+      </c>
+      <c r="N56">
+        <v>-388.1443824000001</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-388.1443824000001</v>
+      </c>
+      <c r="Q56">
+        <v>-386.7943824000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1858191169227167</v>
+      </c>
+      <c r="T56">
+        <v>2.172831829475531</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.2388</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1265767575553403</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2164287937844497</v>
+      </c>
+      <c r="C57">
+        <v>-561.7182613063453</v>
+      </c>
+      <c r="D57">
+        <v>1302.491738693655</v>
+      </c>
+      <c r="E57">
+        <v>1879.61</v>
+      </c>
+      <c r="F57">
+        <v>1895.41</v>
+      </c>
+      <c r="G57">
+        <v>31.2</v>
+      </c>
+      <c r="H57">
+        <v>3430.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>57.6</v>
+      </c>
+      <c r="K57">
+        <v>1.35</v>
+      </c>
+      <c r="L57">
+        <v>56.25</v>
+      </c>
+      <c r="M57">
+        <v>452.6239080000001</v>
+      </c>
+      <c r="N57">
+        <v>-396.3739080000001</v>
+      </c>
+      <c r="O57">
+        <v>-0</v>
+      </c>
+      <c r="P57">
+        <v>-396.3739080000001</v>
+      </c>
+      <c r="Q57">
+        <v>-395.0239080000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1890862084098882</v>
+      </c>
+      <c r="T57">
+        <v>2.221116981241654</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.2388</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.124275361963425</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2184287937844497</v>
+      </c>
+      <c r="C58">
+        <v>-610.6822986607422</v>
+      </c>
+      <c r="D58">
+        <v>1287.989701339258</v>
+      </c>
+      <c r="E58">
+        <v>1914.072</v>
+      </c>
+      <c r="F58">
+        <v>1929.872</v>
+      </c>
+      <c r="G58">
+        <v>31.2</v>
+      </c>
+      <c r="H58">
+        <v>3430.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>57.6</v>
+      </c>
+      <c r="K58">
+        <v>1.35</v>
+      </c>
+      <c r="L58">
+        <v>56.25</v>
+      </c>
+      <c r="M58">
+        <v>460.8534336000001</v>
+      </c>
+      <c r="N58">
+        <v>-404.6034336000001</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-404.6034336000001</v>
+      </c>
+      <c r="Q58">
+        <v>-403.2534336000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1925018040555675</v>
+      </c>
+      <c r="T58">
+        <v>2.27159691263351</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.2388</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.122056159071221</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2204287937844497</v>
+      </c>
+      <c r="C59">
+        <v>-659.3269585188239</v>
+      </c>
+      <c r="D59">
+        <v>1273.807041481176</v>
+      </c>
+      <c r="E59">
+        <v>1948.534</v>
+      </c>
+      <c r="F59">
+        <v>1964.334</v>
+      </c>
+      <c r="G59">
+        <v>31.2</v>
+      </c>
+      <c r="H59">
+        <v>3430.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>57.6</v>
+      </c>
+      <c r="K59">
+        <v>1.35</v>
+      </c>
+      <c r="L59">
+        <v>56.25</v>
+      </c>
+      <c r="M59">
+        <v>469.0829592000001</v>
+      </c>
+      <c r="N59">
+        <v>-412.8329592000001</v>
+      </c>
+      <c r="O59">
+        <v>-0</v>
+      </c>
+      <c r="P59">
+        <v>-412.8329592000001</v>
+      </c>
+      <c r="Q59">
+        <v>-411.4829592000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1960762646149993</v>
+      </c>
+      <c r="T59">
+        <v>2.324424747811034</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.2388</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1199148229471645</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2224287937844497</v>
+      </c>
+      <c r="C60">
+        <v>-707.662676417079</v>
+      </c>
+      <c r="D60">
+        <v>1259.933323582921</v>
+      </c>
+      <c r="E60">
+        <v>1982.996</v>
+      </c>
+      <c r="F60">
+        <v>1998.796</v>
+      </c>
+      <c r="G60">
+        <v>31.2</v>
+      </c>
+      <c r="H60">
+        <v>3430.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>57.6</v>
+      </c>
+      <c r="K60">
+        <v>1.35</v>
+      </c>
+      <c r="L60">
+        <v>56.25</v>
+      </c>
+      <c r="M60">
+        <v>477.3124848</v>
+      </c>
+      <c r="N60">
+        <v>-421.0624848</v>
+      </c>
+      <c r="O60">
+        <v>-0</v>
+      </c>
+      <c r="P60">
+        <v>-421.0624848</v>
+      </c>
+      <c r="Q60">
+        <v>-419.7124848</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.199820937582023</v>
+      </c>
+      <c r="T60">
+        <v>2.379768194187486</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.2388</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1178473259997996</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2244287937844497</v>
+      </c>
+      <c r="C61">
+        <v>-755.6994381541608</v>
+      </c>
+      <c r="D61">
+        <v>1246.358561845839</v>
+      </c>
+      <c r="E61">
+        <v>2017.458</v>
+      </c>
+      <c r="F61">
+        <v>2033.258</v>
+      </c>
+      <c r="G61">
+        <v>31.2</v>
+      </c>
+      <c r="H61">
+        <v>3430.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>57.6</v>
+      </c>
+      <c r="K61">
+        <v>1.35</v>
+      </c>
+      <c r="L61">
+        <v>56.25</v>
+      </c>
+      <c r="M61">
+        <v>485.5420104</v>
+      </c>
+      <c r="N61">
+        <v>-429.2920104</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-429.2920104</v>
+      </c>
+      <c r="Q61">
+        <v>-427.9420104</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.203748277523048</v>
+      </c>
+      <c r="T61">
+        <v>2.437811320874986</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.2388</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1158499136947183</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2264287937844497</v>
+      </c>
+      <c r="C62">
+        <v>-803.4468037604411</v>
+      </c>
+      <c r="D62">
+        <v>1233.073196239559</v>
+      </c>
+      <c r="E62">
+        <v>2051.92</v>
+      </c>
+      <c r="F62">
+        <v>2067.72</v>
+      </c>
+      <c r="G62">
+        <v>31.2</v>
+      </c>
+      <c r="H62">
+        <v>3430.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>57.6</v>
+      </c>
+      <c r="K62">
+        <v>1.35</v>
+      </c>
+      <c r="L62">
+        <v>56.25</v>
+      </c>
+      <c r="M62">
+        <v>493.7715360000001</v>
+      </c>
+      <c r="N62">
+        <v>-437.5215360000001</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-437.5215360000001</v>
+      </c>
+      <c r="Q62">
+        <v>-436.1715360000001</v>
+      </c>
+      <c r="R62">
         <v>1.5</v>
       </c>
-      <c r="AH3">
-        <v>0.6270136307311028</v>
-      </c>
-      <c r="AI3">
-        <v>0.6148238153098421</v>
-      </c>
-      <c r="AJ3">
-        <v>0.04746835443037974</v>
-      </c>
-      <c r="AK3">
-        <v>0.04518072289156626</v>
-      </c>
-      <c r="AL3">
-        <v>4.68</v>
-      </c>
-      <c r="AM3">
-        <v>4.326</v>
-      </c>
-      <c r="AN3">
-        <v>-0.5863267670915412</v>
-      </c>
-      <c r="AO3">
-        <v>-19.76495726495727</v>
-      </c>
-      <c r="AP3">
-        <v>-0.01738122827346466</v>
-      </c>
-      <c r="AQ3">
-        <v>-21.38233934350439</v>
+      <c r="S62">
+        <v>0.2078719844611242</v>
+      </c>
+      <c r="T62">
+        <v>2.498756603896861</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.2388</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1139190817998063</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2284287937844497</v>
+      </c>
+      <c r="C63">
+        <v>-850.9139299507303</v>
+      </c>
+      <c r="D63">
+        <v>1220.06807004927</v>
+      </c>
+      <c r="E63">
+        <v>2086.382</v>
+      </c>
+      <c r="F63">
+        <v>2102.182</v>
+      </c>
+      <c r="G63">
+        <v>31.2</v>
+      </c>
+      <c r="H63">
+        <v>3430.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>57.6</v>
+      </c>
+      <c r="K63">
+        <v>1.35</v>
+      </c>
+      <c r="L63">
+        <v>56.25</v>
+      </c>
+      <c r="M63">
+        <v>502.0010616000001</v>
+      </c>
+      <c r="N63">
+        <v>-445.7510616000001</v>
+      </c>
+      <c r="O63">
+        <v>-0</v>
+      </c>
+      <c r="P63">
+        <v>-445.7510616000001</v>
+      </c>
+      <c r="Q63">
+        <v>-444.4010616</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.212207163549871</v>
+      </c>
+      <c r="T63">
+        <v>2.562827286048062</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.2388</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1120515558686619</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2304287937844497</v>
+      </c>
+      <c r="C64">
+        <v>-898.1095911709917</v>
+      </c>
+      <c r="D64">
+        <v>1207.334408829008</v>
+      </c>
+      <c r="E64">
+        <v>2120.844</v>
+      </c>
+      <c r="F64">
+        <v>2136.644</v>
+      </c>
+      <c r="G64">
+        <v>31.2</v>
+      </c>
+      <c r="H64">
+        <v>3430.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>57.6</v>
+      </c>
+      <c r="K64">
+        <v>1.35</v>
+      </c>
+      <c r="L64">
+        <v>56.25</v>
+      </c>
+      <c r="M64">
+        <v>510.2305872000001</v>
+      </c>
+      <c r="N64">
+        <v>-453.9805872000001</v>
+      </c>
+      <c r="O64">
+        <v>-0</v>
+      </c>
+      <c r="P64">
+        <v>-453.9805872000001</v>
+      </c>
+      <c r="Q64">
+        <v>-452.6305872</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2167705099590781</v>
+      </c>
+      <c r="T64">
+        <v>2.630270109365116</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.2388</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.11024427270949</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2324287937844497</v>
+      </c>
+      <c r="C65">
+        <v>-945.0421993406942</v>
+      </c>
+      <c r="D65">
+        <v>1194.863800659306</v>
+      </c>
+      <c r="E65">
+        <v>2155.306</v>
+      </c>
+      <c r="F65">
+        <v>2171.106</v>
+      </c>
+      <c r="G65">
+        <v>31.2</v>
+      </c>
+      <c r="H65">
+        <v>3430.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>57.6</v>
+      </c>
+      <c r="K65">
+        <v>1.35</v>
+      </c>
+      <c r="L65">
+        <v>56.25</v>
+      </c>
+      <c r="M65">
+        <v>518.4601128</v>
+      </c>
+      <c r="N65">
+        <v>-462.2101128</v>
+      </c>
+      <c r="O65">
+        <v>-0</v>
+      </c>
+      <c r="P65">
+        <v>-462.2101128</v>
+      </c>
+      <c r="Q65">
+        <v>-460.8601128</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2215805237417559</v>
+      </c>
+      <c r="T65">
+        <v>2.701358490699309</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.2388</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1084943636188631</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2344287937844497</v>
+      </c>
+      <c r="C66">
+        <v>-991.7198223841592</v>
+      </c>
+      <c r="D66">
+        <v>1182.648177615841</v>
+      </c>
+      <c r="E66">
+        <v>2189.768</v>
+      </c>
+      <c r="F66">
+        <v>2205.568</v>
+      </c>
+      <c r="G66">
+        <v>31.2</v>
+      </c>
+      <c r="H66">
+        <v>3430.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>57.6</v>
+      </c>
+      <c r="K66">
+        <v>1.35</v>
+      </c>
+      <c r="L66">
+        <v>56.25</v>
+      </c>
+      <c r="M66">
+        <v>526.6896384</v>
+      </c>
+      <c r="N66">
+        <v>-470.4396384</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-470.4396384</v>
+      </c>
+      <c r="Q66">
+        <v>-469.0896384</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2266577605123603</v>
+      </c>
+      <c r="T66">
+        <v>2.776396226552067</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.2388</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1067991391873184</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2364287937844497</v>
+      </c>
+      <c r="C67">
+        <v>-1038.150201636686</v>
+      </c>
+      <c r="D67">
+        <v>1170.679798363314</v>
+      </c>
+      <c r="E67">
+        <v>2224.23</v>
+      </c>
+      <c r="F67">
+        <v>2240.03</v>
+      </c>
+      <c r="G67">
+        <v>31.2</v>
+      </c>
+      <c r="H67">
+        <v>3430.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>57.6</v>
+      </c>
+      <c r="K67">
+        <v>1.35</v>
+      </c>
+      <c r="L67">
+        <v>56.25</v>
+      </c>
+      <c r="M67">
+        <v>534.919164</v>
+      </c>
+      <c r="N67">
+        <v>-478.669164</v>
+      </c>
+      <c r="O67">
+        <v>-0</v>
+      </c>
+      <c r="P67">
+        <v>-478.669164</v>
+      </c>
+      <c r="Q67">
+        <v>-477.319164</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2320251250984277</v>
+      </c>
+      <c r="T67">
+        <v>2.855721833024984</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.2388</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1051560755075135</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2384287937844497</v>
+      </c>
+      <c r="C68">
+        <v>-1084.340768204366</v>
+      </c>
+      <c r="D68">
+        <v>1158.951231795634</v>
+      </c>
+      <c r="E68">
+        <v>2258.692</v>
+      </c>
+      <c r="F68">
+        <v>2274.492</v>
+      </c>
+      <c r="G68">
+        <v>31.2</v>
+      </c>
+      <c r="H68">
+        <v>3430.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>57.6</v>
+      </c>
+      <c r="K68">
+        <v>1.35</v>
+      </c>
+      <c r="L68">
+        <v>56.25</v>
+      </c>
+      <c r="M68">
+        <v>543.1486896000001</v>
+      </c>
+      <c r="N68">
+        <v>-486.8986896000001</v>
+      </c>
+      <c r="O68">
+        <v>-0</v>
+      </c>
+      <c r="P68">
+        <v>-486.8986896000001</v>
+      </c>
+      <c r="Q68">
+        <v>-485.5486896000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2377082170130873</v>
+      </c>
+      <c r="T68">
+        <v>2.939713651643366</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.2388</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1035628016361875</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2404287937844497</v>
+      </c>
+      <c r="C69">
+        <v>-1130.298658350241</v>
+      </c>
+      <c r="D69">
+        <v>1147.455341649759</v>
+      </c>
+      <c r="E69">
+        <v>2293.154</v>
+      </c>
+      <c r="F69">
+        <v>2308.954</v>
+      </c>
+      <c r="G69">
+        <v>31.2</v>
+      </c>
+      <c r="H69">
+        <v>3430.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>57.6</v>
+      </c>
+      <c r="K69">
+        <v>1.35</v>
+      </c>
+      <c r="L69">
+        <v>56.25</v>
+      </c>
+      <c r="M69">
+        <v>551.3782152000001</v>
+      </c>
+      <c r="N69">
+        <v>-495.1282152000001</v>
+      </c>
+      <c r="O69">
+        <v>-0</v>
+      </c>
+      <c r="P69">
+        <v>-495.1282152000001</v>
+      </c>
+      <c r="Q69">
+        <v>-493.7782152000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2437357387407567</v>
+      </c>
+      <c r="T69">
+        <v>3.028795883511346</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.2388</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.102017088178931</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2424287937844497</v>
+      </c>
+      <c r="C70">
+        <v>-1176.030727973738</v>
+      </c>
+      <c r="D70">
+        <v>1136.185272026262</v>
+      </c>
+      <c r="E70">
+        <v>2327.616</v>
+      </c>
+      <c r="F70">
+        <v>2343.416</v>
+      </c>
+      <c r="G70">
+        <v>31.2</v>
+      </c>
+      <c r="H70">
+        <v>3430.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>57.6</v>
+      </c>
+      <c r="K70">
+        <v>1.35</v>
+      </c>
+      <c r="L70">
+        <v>56.25</v>
+      </c>
+      <c r="M70">
+        <v>559.6077408000001</v>
+      </c>
+      <c r="N70">
+        <v>-503.3577408000001</v>
+      </c>
+      <c r="O70">
+        <v>-0</v>
+      </c>
+      <c r="P70">
+        <v>-503.3577408000001</v>
+      </c>
+      <c r="Q70">
+        <v>-502.0077408000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2501399805764053</v>
+      </c>
+      <c r="T70">
+        <v>3.123445754871076</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.2388</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.100516836882182</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2444287937844497</v>
+      </c>
+      <c r="C71">
+        <v>-1221.543566245127</v>
+      </c>
+      <c r="D71">
+        <v>1125.134433754874</v>
+      </c>
+      <c r="E71">
+        <v>2362.078</v>
+      </c>
+      <c r="F71">
+        <v>2377.878000000001</v>
+      </c>
+      <c r="G71">
+        <v>31.2</v>
+      </c>
+      <c r="H71">
+        <v>3430.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>57.6</v>
+      </c>
+      <c r="K71">
+        <v>1.35</v>
+      </c>
+      <c r="L71">
+        <v>56.25</v>
+      </c>
+      <c r="M71">
+        <v>567.8372664000002</v>
+      </c>
+      <c r="N71">
+        <v>-511.5872664000002</v>
+      </c>
+      <c r="O71">
+        <v>-0</v>
+      </c>
+      <c r="P71">
+        <v>-511.5872664000002</v>
+      </c>
+      <c r="Q71">
+        <v>-510.2372664000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2569573993046764</v>
+      </c>
+      <c r="T71">
+        <v>3.224202069544337</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.2388</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.09906007113026627</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2464287937844497</v>
+      </c>
+      <c r="C72">
+        <v>-1266.843508451957</v>
+      </c>
+      <c r="D72">
+        <v>1114.296491548044</v>
+      </c>
+      <c r="E72">
+        <v>2396.54</v>
+      </c>
+      <c r="F72">
+        <v>2412.340000000001</v>
+      </c>
+      <c r="G72">
+        <v>31.2</v>
+      </c>
+      <c r="H72">
+        <v>3430.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>57.6</v>
+      </c>
+      <c r="K72">
+        <v>1.35</v>
+      </c>
+      <c r="L72">
+        <v>56.25</v>
+      </c>
+      <c r="M72">
+        <v>576.0667920000002</v>
+      </c>
+      <c r="N72">
+        <v>-519.8167920000002</v>
+      </c>
+      <c r="O72">
+        <v>-0</v>
+      </c>
+      <c r="P72">
+        <v>-519.8167920000002</v>
+      </c>
+      <c r="Q72">
+        <v>-518.4667920000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2642293126148323</v>
+      </c>
+      <c r="T72">
+        <v>3.331675471862481</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.2388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.09764492725697682</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2484287937844497</v>
+      </c>
+      <c r="C73">
+        <v>-1311.936648110126</v>
+      </c>
+      <c r="D73">
+        <v>1103.665351889875</v>
+      </c>
+      <c r="E73">
+        <v>2431.002</v>
+      </c>
+      <c r="F73">
+        <v>2446.802</v>
+      </c>
+      <c r="G73">
+        <v>31.2</v>
+      </c>
+      <c r="H73">
+        <v>3430.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>57.6</v>
+      </c>
+      <c r="K73">
+        <v>1.35</v>
+      </c>
+      <c r="L73">
+        <v>56.25</v>
+      </c>
+      <c r="M73">
+        <v>584.2963176000001</v>
+      </c>
+      <c r="N73">
+        <v>-528.0463176000001</v>
+      </c>
+      <c r="O73">
+        <v>-0</v>
+      </c>
+      <c r="P73">
+        <v>-528.0463176000001</v>
+      </c>
+      <c r="Q73">
+        <v>-526.6963176</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2720027371877576</v>
+      </c>
+      <c r="T73">
+        <v>3.446560832961187</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.2388</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.09626964659138559</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2504287937844497</v>
+      </c>
+      <c r="C74">
+        <v>-1356.828848388203</v>
+      </c>
+      <c r="D74">
+        <v>1093.235151611797</v>
+      </c>
+      <c r="E74">
+        <v>2465.464</v>
+      </c>
+      <c r="F74">
+        <v>2481.264</v>
+      </c>
+      <c r="G74">
+        <v>31.2</v>
+      </c>
+      <c r="H74">
+        <v>3430.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>57.6</v>
+      </c>
+      <c r="K74">
+        <v>1.35</v>
+      </c>
+      <c r="L74">
+        <v>56.25</v>
+      </c>
+      <c r="M74">
+        <v>592.5258432000001</v>
+      </c>
+      <c r="N74">
+        <v>-536.2758432000001</v>
+      </c>
+      <c r="O74">
+        <v>-0</v>
+      </c>
+      <c r="P74">
+        <v>-536.2758432000001</v>
+      </c>
+      <c r="Q74">
+        <v>-534.9258432</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2803314063730346</v>
+      </c>
+      <c r="T74">
+        <v>3.569652291281229</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.2388</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.09493256816650519</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2524287937844497</v>
+      </c>
+      <c r="C75">
+        <v>-1401.525752890027</v>
+      </c>
+      <c r="D75">
+        <v>1083.000247109973</v>
+      </c>
+      <c r="E75">
+        <v>2499.926</v>
+      </c>
+      <c r="F75">
+        <v>2515.726</v>
+      </c>
+      <c r="G75">
+        <v>31.2</v>
+      </c>
+      <c r="H75">
+        <v>3430.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>57.6</v>
+      </c>
+      <c r="K75">
+        <v>1.35</v>
+      </c>
+      <c r="L75">
+        <v>56.25</v>
+      </c>
+      <c r="M75">
+        <v>600.7553688</v>
+      </c>
+      <c r="N75">
+        <v>-544.5053688</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
+        <v>-544.5053688</v>
+      </c>
+      <c r="Q75">
+        <v>-543.1553688</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2892770140164803</v>
+      </c>
+      <c r="T75">
+        <v>3.701861635402756</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.2388</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.09363212202723803</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2544287937844497</v>
+      </c>
+      <c r="C76">
+        <v>-1446.032795837237</v>
+      </c>
+      <c r="D76">
+        <v>1072.955204162763</v>
+      </c>
+      <c r="E76">
+        <v>2534.388</v>
+      </c>
+      <c r="F76">
+        <v>2550.188</v>
+      </c>
+      <c r="G76">
+        <v>31.2</v>
+      </c>
+      <c r="H76">
+        <v>3430.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>57.6</v>
+      </c>
+      <c r="K76">
+        <v>1.35</v>
+      </c>
+      <c r="L76">
+        <v>56.25</v>
+      </c>
+      <c r="M76">
+        <v>608.9848944</v>
+      </c>
+      <c r="N76">
+        <v>-552.7348944</v>
+      </c>
+      <c r="O76">
+        <v>-0</v>
+      </c>
+      <c r="P76">
+        <v>-552.7348944</v>
+      </c>
+      <c r="Q76">
+        <v>-551.3848944</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2989107453248064</v>
+      </c>
+      <c r="T76">
+        <v>3.844240929072093</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.2388</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.09236682308092403</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2564287937844497</v>
+      </c>
+      <c r="C77">
+        <v>-1490.355211690347</v>
+      </c>
+      <c r="D77">
+        <v>1063.094788309653</v>
+      </c>
+      <c r="E77">
+        <v>2568.85</v>
+      </c>
+      <c r="F77">
+        <v>2584.65</v>
+      </c>
+      <c r="G77">
+        <v>31.2</v>
+      </c>
+      <c r="H77">
+        <v>3430.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>57.6</v>
+      </c>
+      <c r="K77">
+        <v>1.35</v>
+      </c>
+      <c r="L77">
+        <v>56.25</v>
+      </c>
+      <c r="M77">
+        <v>617.21442</v>
+      </c>
+      <c r="N77">
+        <v>-560.96442</v>
+      </c>
+      <c r="O77">
+        <v>-0</v>
+      </c>
+      <c r="P77">
+        <v>-560.96442</v>
+      </c>
+      <c r="Q77">
+        <v>-559.61442</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3093151751377988</v>
+      </c>
+      <c r="T77">
+        <v>3.998010566234977</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.2388</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.09113526543984507</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2584287937844497</v>
+      </c>
+      <c r="C78">
+        <v>-1534.498044244143</v>
+      </c>
+      <c r="D78">
+        <v>1053.413955755857</v>
+      </c>
+      <c r="E78">
+        <v>2603.312</v>
+      </c>
+      <c r="F78">
+        <v>2619.112</v>
+      </c>
+      <c r="G78">
+        <v>31.2</v>
+      </c>
+      <c r="H78">
+        <v>3430.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>57.6</v>
+      </c>
+      <c r="K78">
+        <v>1.35</v>
+      </c>
+      <c r="L78">
+        <v>56.25</v>
+      </c>
+      <c r="M78">
+        <v>625.4439456</v>
+      </c>
+      <c r="N78">
+        <v>-569.1939456</v>
+      </c>
+      <c r="O78">
+        <v>-0</v>
+      </c>
+      <c r="P78">
+        <v>-569.1939456</v>
+      </c>
+      <c r="Q78">
+        <v>-567.8439456</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3205866407685404</v>
+      </c>
+      <c r="T78">
+        <v>4.164594339828101</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.2388</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.08993611721037342</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2604287937844497</v>
+      </c>
+      <c r="C79">
+        <v>-1578.46615523061</v>
+      </c>
+      <c r="D79">
+        <v>1043.90784476939</v>
+      </c>
+      <c r="E79">
+        <v>2637.774</v>
+      </c>
+      <c r="F79">
+        <v>2653.574</v>
+      </c>
+      <c r="G79">
+        <v>31.2</v>
+      </c>
+      <c r="H79">
+        <v>3430.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>57.6</v>
+      </c>
+      <c r="K79">
+        <v>1.35</v>
+      </c>
+      <c r="L79">
+        <v>56.25</v>
+      </c>
+      <c r="M79">
+        <v>633.6734712</v>
+      </c>
+      <c r="N79">
+        <v>-577.4234712</v>
+      </c>
+      <c r="O79">
+        <v>-0</v>
+      </c>
+      <c r="P79">
+        <v>-577.4234712</v>
+      </c>
+      <c r="Q79">
+        <v>-576.0734712</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3328382338454334</v>
+      </c>
+      <c r="T79">
+        <v>4.345663658951062</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.2388</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.08876811568816079</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2624287937844497</v>
+      </c>
+      <c r="C80">
+        <v>-1622.264232460232</v>
+      </c>
+      <c r="D80">
+        <v>1034.571767539769</v>
+      </c>
+      <c r="E80">
+        <v>2672.236</v>
+      </c>
+      <c r="F80">
+        <v>2688.036000000001</v>
+      </c>
+      <c r="G80">
+        <v>31.2</v>
+      </c>
+      <c r="H80">
+        <v>3430.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>57.6</v>
+      </c>
+      <c r="K80">
+        <v>1.35</v>
+      </c>
+      <c r="L80">
+        <v>56.25</v>
+      </c>
+      <c r="M80">
+        <v>641.9029968000002</v>
+      </c>
+      <c r="N80">
+        <v>-585.6529968000002</v>
+      </c>
+      <c r="O80">
+        <v>-0</v>
+      </c>
+      <c r="P80">
+        <v>-585.6529968000002</v>
+      </c>
+      <c r="Q80">
+        <v>-584.3029968000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.346203608111135</v>
+      </c>
+      <c r="T80">
+        <v>4.54319382526702</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.2388</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.08763006292292785</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2644287937844497</v>
+      </c>
+      <c r="C81">
+        <v>-1665.896797530292</v>
+      </c>
+      <c r="D81">
+        <v>1025.401202469708</v>
+      </c>
+      <c r="E81">
+        <v>2706.698</v>
+      </c>
+      <c r="F81">
+        <v>2722.498000000001</v>
+      </c>
+      <c r="G81">
+        <v>31.2</v>
+      </c>
+      <c r="H81">
+        <v>3430.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>57.6</v>
+      </c>
+      <c r="K81">
+        <v>1.35</v>
+      </c>
+      <c r="L81">
+        <v>56.25</v>
+      </c>
+      <c r="M81">
+        <v>650.1325224000002</v>
+      </c>
+      <c r="N81">
+        <v>-593.8825224000002</v>
+      </c>
+      <c r="O81">
+        <v>-0</v>
+      </c>
+      <c r="P81">
+        <v>-593.8825224000002</v>
+      </c>
+      <c r="Q81">
+        <v>-592.5325224000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3608418751640462</v>
+      </c>
+      <c r="T81">
+        <v>4.759536388374974</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.2388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.08652082162010599</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2664287937844497</v>
+      </c>
+      <c r="C82">
+        <v>-1709.368213126816</v>
+      </c>
+      <c r="D82">
+        <v>1016.391786873185</v>
+      </c>
+      <c r="E82">
+        <v>2741.16</v>
+      </c>
+      <c r="F82">
+        <v>2756.96</v>
+      </c>
+      <c r="G82">
+        <v>31.2</v>
+      </c>
+      <c r="H82">
+        <v>3430.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>57.6</v>
+      </c>
+      <c r="K82">
+        <v>1.35</v>
+      </c>
+      <c r="L82">
+        <v>56.25</v>
+      </c>
+      <c r="M82">
+        <v>658.3620480000002</v>
+      </c>
+      <c r="N82">
+        <v>-602.1120480000002</v>
+      </c>
+      <c r="O82">
+        <v>-0</v>
+      </c>
+      <c r="P82">
+        <v>-602.1120480000002</v>
+      </c>
+      <c r="Q82">
+        <v>-600.7620480000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3769439689222485</v>
+      </c>
+      <c r="T82">
+        <v>4.997513207793722</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.2388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.08543931134985472</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2684287937844497</v>
+      </c>
+      <c r="C83">
+        <v>-1752.682689944921</v>
+      </c>
+      <c r="D83">
+        <v>1007.539310055079</v>
+      </c>
+      <c r="E83">
+        <v>2775.622</v>
+      </c>
+      <c r="F83">
+        <v>2791.422</v>
+      </c>
+      <c r="G83">
+        <v>31.2</v>
+      </c>
+      <c r="H83">
+        <v>3430.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>57.6</v>
+      </c>
+      <c r="K83">
+        <v>1.35</v>
+      </c>
+      <c r="L83">
+        <v>56.25</v>
+      </c>
+      <c r="M83">
+        <v>666.5915736000002</v>
+      </c>
+      <c r="N83">
+        <v>-610.3415736000002</v>
+      </c>
+      <c r="O83">
+        <v>-0</v>
+      </c>
+      <c r="P83">
+        <v>-610.3415736000002</v>
+      </c>
+      <c r="Q83">
+        <v>-608.9915736000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3947410199181563</v>
+      </c>
+      <c r="T83">
+        <v>5.260540218730234</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.2388</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.08438450503689354</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2704287937844497</v>
+      </c>
+      <c r="C84">
+        <v>-1795.844293250654</v>
+      </c>
+      <c r="D84">
+        <v>998.8397067493463</v>
+      </c>
+      <c r="E84">
+        <v>2810.084</v>
+      </c>
+      <c r="F84">
+        <v>2825.884</v>
+      </c>
+      <c r="G84">
+        <v>31.2</v>
+      </c>
+      <c r="H84">
+        <v>3430.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>57.6</v>
+      </c>
+      <c r="K84">
+        <v>1.35</v>
+      </c>
+      <c r="L84">
+        <v>56.25</v>
+      </c>
+      <c r="M84">
+        <v>674.8210992000002</v>
+      </c>
+      <c r="N84">
+        <v>-618.5710992000002</v>
+      </c>
+      <c r="O84">
+        <v>-0</v>
+      </c>
+      <c r="P84">
+        <v>-618.5710992000002</v>
+      </c>
+      <c r="Q84">
+        <v>-617.2210992000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4145155210247206</v>
+      </c>
+      <c r="T84">
+        <v>5.552792453104137</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.2388</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.08335542570717536</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2724287937844497</v>
+      </c>
+      <c r="C85">
+        <v>-1838.856949105779</v>
+      </c>
+      <c r="D85">
+        <v>990.2890508942216</v>
+      </c>
+      <c r="E85">
+        <v>2844.546</v>
+      </c>
+      <c r="F85">
+        <v>2860.346</v>
+      </c>
+      <c r="G85">
+        <v>31.2</v>
+      </c>
+      <c r="H85">
+        <v>3430.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>57.6</v>
+      </c>
+      <c r="K85">
+        <v>1.35</v>
+      </c>
+      <c r="L85">
+        <v>56.25</v>
+      </c>
+      <c r="M85">
+        <v>683.0506248000002</v>
+      </c>
+      <c r="N85">
+        <v>-626.8006248000002</v>
+      </c>
+      <c r="O85">
+        <v>-0</v>
+      </c>
+      <c r="P85">
+        <v>-626.8006248000002</v>
+      </c>
+      <c r="Q85">
+        <v>-625.4506248000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4366164340261748</v>
+      </c>
+      <c r="T85">
+        <v>5.879427303286733</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.2388</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.08235114346973949</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2744287937844497</v>
+      </c>
+      <c r="C86">
+        <v>-1881.724450275555</v>
+      </c>
+      <c r="D86">
+        <v>981.8835497244446</v>
+      </c>
+      <c r="E86">
+        <v>2879.008</v>
+      </c>
+      <c r="F86">
+        <v>2894.808</v>
+      </c>
+      <c r="G86">
+        <v>31.2</v>
+      </c>
+      <c r="H86">
+        <v>3430.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>57.6</v>
+      </c>
+      <c r="K86">
+        <v>1.35</v>
+      </c>
+      <c r="L86">
+        <v>56.25</v>
+      </c>
+      <c r="M86">
+        <v>691.2801504</v>
+      </c>
+      <c r="N86">
+        <v>-635.0301504</v>
+      </c>
+      <c r="O86">
+        <v>-0</v>
+      </c>
+      <c r="P86">
+        <v>-635.0301504</v>
+      </c>
+      <c r="Q86">
+        <v>-633.6801504</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4614799611528105</v>
+      </c>
+      <c r="T86">
+        <v>6.24689150974215</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.2388</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.08137077271414739</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2764287937844497</v>
+      </c>
+      <c r="C87">
+        <v>-1924.450461838187</v>
+      </c>
+      <c r="D87">
+        <v>973.6195381618129</v>
+      </c>
+      <c r="E87">
+        <v>2913.47</v>
+      </c>
+      <c r="F87">
+        <v>2929.27</v>
+      </c>
+      <c r="G87">
+        <v>31.2</v>
+      </c>
+      <c r="H87">
+        <v>3430.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>57.6</v>
+      </c>
+      <c r="K87">
+        <v>1.35</v>
+      </c>
+      <c r="L87">
+        <v>56.25</v>
+      </c>
+      <c r="M87">
+        <v>699.509676</v>
+      </c>
+      <c r="N87">
+        <v>-643.259676</v>
+      </c>
+      <c r="O87">
+        <v>-0</v>
+      </c>
+      <c r="P87">
+        <v>-643.259676</v>
+      </c>
+      <c r="Q87">
+        <v>-641.909676</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4896586252296645</v>
+      </c>
+      <c r="T87">
+        <v>6.663350943724961</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.2388</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.08041346950574557</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2784287937844497</v>
+      </c>
+      <c r="C88">
+        <v>-1967.038526513349</v>
+      </c>
+      <c r="D88">
+        <v>965.4934734866506</v>
+      </c>
+      <c r="E88">
+        <v>2947.932</v>
+      </c>
+      <c r="F88">
+        <v>2963.732</v>
+      </c>
+      <c r="G88">
+        <v>31.2</v>
+      </c>
+      <c r="H88">
+        <v>3430.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>57.6</v>
+      </c>
+      <c r="K88">
+        <v>1.35</v>
+      </c>
+      <c r="L88">
+        <v>56.25</v>
+      </c>
+      <c r="M88">
+        <v>707.7392016</v>
+      </c>
+      <c r="N88">
+        <v>-651.4892016</v>
+      </c>
+      <c r="O88">
+        <v>-0</v>
+      </c>
+      <c r="P88">
+        <v>-651.4892016</v>
+      </c>
+      <c r="Q88">
+        <v>-650.1392016</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5218628127460692</v>
+      </c>
+      <c r="T88">
+        <v>7.139304582562459</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.2388</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.07947842916265557</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2804287937844497</v>
+      </c>
+      <c r="C89">
+        <v>-2009.492069726101</v>
+      </c>
+      <c r="D89">
+        <v>957.5019302738997</v>
+      </c>
+      <c r="E89">
+        <v>2982.394</v>
+      </c>
+      <c r="F89">
+        <v>2998.194</v>
+      </c>
+      <c r="G89">
+        <v>31.2</v>
+      </c>
+      <c r="H89">
+        <v>3430.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>57.6</v>
+      </c>
+      <c r="K89">
+        <v>1.35</v>
+      </c>
+      <c r="L89">
+        <v>56.25</v>
+      </c>
+      <c r="M89">
+        <v>715.9687272000001</v>
+      </c>
+      <c r="N89">
+        <v>-659.7187272000001</v>
+      </c>
+      <c r="O89">
+        <v>-0</v>
+      </c>
+      <c r="P89">
+        <v>-659.7187272000001</v>
+      </c>
+      <c r="Q89">
+        <v>-658.3687272000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5590214906496129</v>
+      </c>
+      <c r="T89">
+        <v>7.688481858144185</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.2388</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.07856488399986639</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2824287937844497</v>
+      </c>
+      <c r="C90">
+        <v>-2051.81440442136</v>
+      </c>
+      <c r="D90">
+        <v>949.641595578641</v>
+      </c>
+      <c r="E90">
+        <v>3016.856</v>
+      </c>
+      <c r="F90">
+        <v>3032.656</v>
+      </c>
+      <c r="G90">
+        <v>31.2</v>
+      </c>
+      <c r="H90">
+        <v>3430.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>57.6</v>
+      </c>
+      <c r="K90">
+        <v>1.35</v>
+      </c>
+      <c r="L90">
+        <v>56.25</v>
+      </c>
+      <c r="M90">
+        <v>724.1982528000001</v>
+      </c>
+      <c r="N90">
+        <v>-667.9482528000001</v>
+      </c>
+      <c r="O90">
+        <v>-0</v>
+      </c>
+      <c r="P90">
+        <v>-667.9482528000001</v>
+      </c>
+      <c r="Q90">
+        <v>-666.5982528000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6023732815370808</v>
+      </c>
+      <c r="T90">
+        <v>8.329188679656202</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.2388</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.07767210122714063</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2844287937844497</v>
+      </c>
+      <c r="C91">
+        <v>-2094.008735643178</v>
+      </c>
+      <c r="D91">
+        <v>941.9092643568221</v>
+      </c>
+      <c r="E91">
+        <v>3051.318</v>
+      </c>
+      <c r="F91">
+        <v>3067.118</v>
+      </c>
+      <c r="G91">
+        <v>31.2</v>
+      </c>
+      <c r="H91">
+        <v>3430.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>57.6</v>
+      </c>
+      <c r="K91">
+        <v>1.35</v>
+      </c>
+      <c r="L91">
+        <v>56.25</v>
+      </c>
+      <c r="M91">
+        <v>732.4277784000001</v>
+      </c>
+      <c r="N91">
+        <v>-676.1777784000001</v>
+      </c>
+      <c r="O91">
+        <v>-0</v>
+      </c>
+      <c r="P91">
+        <v>-676.1777784000001</v>
+      </c>
+      <c r="Q91">
+        <v>-674.8277784000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6536072162222699</v>
+      </c>
+      <c r="T91">
+        <v>9.086387650534039</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.2388</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.07679938098863348</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2864287937844497</v>
+      </c>
+      <c r="C92">
+        <v>-2136.078164892111</v>
+      </c>
+      <c r="D92">
+        <v>934.3018351078897</v>
+      </c>
+      <c r="E92">
+        <v>3085.78</v>
+      </c>
+      <c r="F92">
+        <v>3101.58</v>
+      </c>
+      <c r="G92">
+        <v>31.2</v>
+      </c>
+      <c r="H92">
+        <v>3430.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>57.6</v>
+      </c>
+      <c r="K92">
+        <v>1.35</v>
+      </c>
+      <c r="L92">
+        <v>56.25</v>
+      </c>
+      <c r="M92">
+        <v>740.6573040000002</v>
+      </c>
+      <c r="N92">
+        <v>-684.4073040000002</v>
+      </c>
+      <c r="O92">
+        <v>-0</v>
+      </c>
+      <c r="P92">
+        <v>-684.4073040000002</v>
+      </c>
+      <c r="Q92">
+        <v>-683.0573040000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.715087937844497</v>
+      </c>
+      <c r="T92">
+        <v>9.995026415587445</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.2388</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.07594605453320413</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2884287937844497</v>
+      </c>
+      <c r="C93">
+        <v>-2178.025694273105</v>
+      </c>
+      <c r="D93">
+        <v>926.8163057268951</v>
+      </c>
+      <c r="E93">
+        <v>3120.242</v>
+      </c>
+      <c r="F93">
+        <v>3136.042</v>
+      </c>
+      <c r="G93">
+        <v>31.2</v>
+      </c>
+      <c r="H93">
+        <v>3430.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>57.6</v>
+      </c>
+      <c r="K93">
+        <v>1.35</v>
+      </c>
+      <c r="L93">
+        <v>56.25</v>
+      </c>
+      <c r="M93">
+        <v>748.8868296000002</v>
+      </c>
+      <c r="N93">
+        <v>-692.6368296000002</v>
+      </c>
+      <c r="O93">
+        <v>-0</v>
+      </c>
+      <c r="P93">
+        <v>-692.6368296000002</v>
+      </c>
+      <c r="Q93">
+        <v>-691.2868296000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7902310420494412</v>
+      </c>
+      <c r="T93">
+        <v>11.10558490620827</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.2388</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.07511148250536681</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2904287937844497</v>
+      </c>
+      <c r="C94">
+        <v>-2219.854230445598</v>
+      </c>
+      <c r="D94">
+        <v>919.4497695544025</v>
+      </c>
+      <c r="E94">
+        <v>3154.704</v>
+      </c>
+      <c r="F94">
+        <v>3170.504</v>
+      </c>
+      <c r="G94">
+        <v>31.2</v>
+      </c>
+      <c r="H94">
+        <v>3430.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>57.6</v>
+      </c>
+      <c r="K94">
+        <v>1.35</v>
+      </c>
+      <c r="L94">
+        <v>56.25</v>
+      </c>
+      <c r="M94">
+        <v>757.1163552000002</v>
+      </c>
+      <c r="N94">
+        <v>-700.8663552000002</v>
+      </c>
+      <c r="O94">
+        <v>-0</v>
+      </c>
+      <c r="P94">
+        <v>-700.8663552000002</v>
+      </c>
+      <c r="Q94">
+        <v>-699.5163552000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8841599223056216</v>
+      </c>
+      <c r="T94">
+        <v>12.49378301948431</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.2388</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.0742950533476997</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2924287937844497</v>
+      </c>
+      <c r="C95">
+        <v>-2261.566588386706</v>
+      </c>
+      <c r="D95">
+        <v>912.1994116132942</v>
+      </c>
+      <c r="E95">
+        <v>3189.166</v>
+      </c>
+      <c r="F95">
+        <v>3204.966</v>
+      </c>
+      <c r="G95">
+        <v>31.2</v>
+      </c>
+      <c r="H95">
+        <v>3430.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>57.6</v>
+      </c>
+      <c r="K95">
+        <v>1.35</v>
+      </c>
+      <c r="L95">
+        <v>56.25</v>
+      </c>
+      <c r="M95">
+        <v>765.3458808000001</v>
+      </c>
+      <c r="N95">
+        <v>-709.0958808000001</v>
+      </c>
+      <c r="O95">
+        <v>-0</v>
+      </c>
+      <c r="P95">
+        <v>-709.0958808000001</v>
+      </c>
+      <c r="Q95">
+        <v>-707.7458808000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.004925625492139</v>
+      </c>
+      <c r="T95">
+        <v>14.27860916512493</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.2388</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.07349618180632667</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2944287937844497</v>
+      </c>
+      <c r="C96">
+        <v>-2303.165494977772</v>
+      </c>
+      <c r="D96">
+        <v>905.062505022228</v>
+      </c>
+      <c r="E96">
+        <v>3223.628</v>
+      </c>
+      <c r="F96">
+        <v>3239.428</v>
+      </c>
+      <c r="G96">
+        <v>31.2</v>
+      </c>
+      <c r="H96">
+        <v>3430.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>57.6</v>
+      </c>
+      <c r="K96">
+        <v>1.35</v>
+      </c>
+      <c r="L96">
+        <v>56.25</v>
+      </c>
+      <c r="M96">
+        <v>773.5754064000001</v>
+      </c>
+      <c r="N96">
+        <v>-717.3254064000001</v>
+      </c>
+      <c r="O96">
+        <v>-0</v>
+      </c>
+      <c r="P96">
+        <v>-717.3254064000001</v>
+      </c>
+      <c r="Q96">
+        <v>-715.9754064000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.165946563074162</v>
+      </c>
+      <c r="T96">
+        <v>16.65837735931242</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.2388</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.0727143075317912</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2964287937844498</v>
+      </c>
+      <c r="C97">
+        <v>-2344.653592423848</v>
+      </c>
+      <c r="D97">
+        <v>898.0364075761524</v>
+      </c>
+      <c r="E97">
+        <v>3258.09</v>
+      </c>
+      <c r="F97">
+        <v>3273.89</v>
+      </c>
+      <c r="G97">
+        <v>31.2</v>
+      </c>
+      <c r="H97">
+        <v>3430.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>57.6</v>
+      </c>
+      <c r="K97">
+        <v>1.35</v>
+      </c>
+      <c r="L97">
+        <v>56.25</v>
+      </c>
+      <c r="M97">
+        <v>781.8049320000001</v>
+      </c>
+      <c r="N97">
+        <v>-725.5549320000001</v>
+      </c>
+      <c r="O97">
+        <v>-0</v>
+      </c>
+      <c r="P97">
+        <v>-725.5549320000001</v>
+      </c>
+      <c r="Q97">
+        <v>-724.2049320000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.391375875688996</v>
+      </c>
+      <c r="T97">
+        <v>19.99005283117491</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.2388</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.07194889376829872</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2984287937844497</v>
+      </c>
+      <c r="C98">
+        <v>-2386.03344151513</v>
+      </c>
+      <c r="D98">
+        <v>891.1185584848706</v>
+      </c>
+      <c r="E98">
+        <v>3292.552</v>
+      </c>
+      <c r="F98">
+        <v>3308.352</v>
+      </c>
+      <c r="G98">
+        <v>31.2</v>
+      </c>
+      <c r="H98">
+        <v>3430.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>57.6</v>
+      </c>
+      <c r="K98">
+        <v>1.35</v>
+      </c>
+      <c r="L98">
+        <v>56.25</v>
+      </c>
+      <c r="M98">
+        <v>790.0344576000001</v>
+      </c>
+      <c r="N98">
+        <v>-733.7844576000001</v>
+      </c>
+      <c r="O98">
+        <v>-0</v>
+      </c>
+      <c r="P98">
+        <v>-733.7844576000001</v>
+      </c>
+      <c r="Q98">
+        <v>-732.4344576000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.729519844611241</v>
+      </c>
+      <c r="T98">
+        <v>24.98756603896858</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.2388</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.07119942612487895</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3004287937844497</v>
+      </c>
+      <c r="C99">
+        <v>-2427.307524738806</v>
+      </c>
+      <c r="D99">
+        <v>884.3064752611945</v>
+      </c>
+      <c r="E99">
+        <v>3327.014</v>
+      </c>
+      <c r="F99">
+        <v>3342.814</v>
+      </c>
+      <c r="G99">
+        <v>31.2</v>
+      </c>
+      <c r="H99">
+        <v>3430.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>57.6</v>
+      </c>
+      <c r="K99">
+        <v>1.35</v>
+      </c>
+      <c r="L99">
+        <v>56.25</v>
+      </c>
+      <c r="M99">
+        <v>798.2639832000001</v>
+      </c>
+      <c r="N99">
+        <v>-742.0139832000001</v>
+      </c>
+      <c r="O99">
+        <v>-0</v>
+      </c>
+      <c r="P99">
+        <v>-742.0139832000001</v>
+      </c>
+      <c r="Q99">
+        <v>-740.6639832000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.293093126148321</v>
+      </c>
+      <c r="T99">
+        <v>33.31675471862478</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.2388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.07046541142256058</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3024287937844497</v>
+      </c>
+      <c r="C100">
+        <v>-2468.478249249257</v>
+      </c>
+      <c r="D100">
+        <v>877.5977507507433</v>
+      </c>
+      <c r="E100">
+        <v>3361.476</v>
+      </c>
+      <c r="F100">
+        <v>3377.276</v>
+      </c>
+      <c r="G100">
+        <v>31.2</v>
+      </c>
+      <c r="H100">
+        <v>3430.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>57.6</v>
+      </c>
+      <c r="K100">
+        <v>1.35</v>
+      </c>
+      <c r="L100">
+        <v>56.25</v>
+      </c>
+      <c r="M100">
+        <v>806.4935088000001</v>
+      </c>
+      <c r="N100">
+        <v>-750.2435088000001</v>
+      </c>
+      <c r="O100">
+        <v>-0</v>
+      </c>
+      <c r="P100">
+        <v>-750.2435088000001</v>
+      </c>
+      <c r="Q100">
+        <v>-748.8935088000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.420239689222482</v>
+      </c>
+      <c r="T100">
+        <v>49.97513207793717</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.2388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.06974637661212635</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3044287937844497</v>
+      </c>
+      <c r="C101">
+        <v>-2509.547949704072</v>
+      </c>
+      <c r="D101">
+        <v>870.9900502959282</v>
+      </c>
+      <c r="E101">
+        <v>3395.938</v>
+      </c>
+      <c r="F101">
+        <v>3411.738</v>
+      </c>
+      <c r="G101">
+        <v>31.2</v>
+      </c>
+      <c r="H101">
+        <v>3430.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>57.6</v>
+      </c>
+      <c r="K101">
+        <v>1.35</v>
+      </c>
+      <c r="L101">
+        <v>56.25</v>
+      </c>
+      <c r="M101">
+        <v>814.7230344000001</v>
+      </c>
+      <c r="N101">
+        <v>-758.4730344000001</v>
+      </c>
+      <c r="O101">
+        <v>-0</v>
+      </c>
+      <c r="P101">
+        <v>-758.4730344000001</v>
+      </c>
+      <c r="Q101">
+        <v>-757.1230344000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.801679378444963</v>
+      </c>
+      <c r="T101">
+        <v>99.95026415587434</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.2388</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.06904186775745835</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
